--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -766,7 +766,7 @@
         <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.95</v>
@@ -796,7 +796,7 @@
         <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
@@ -805,7 +805,7 @@
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
         <v>2.84</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1539,13 +1539,13 @@
         <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
         <v>3.25</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
         <v>3.05</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,46 +763,46 @@
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
         <v>2.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.71</v>
@@ -811,116 +811,116 @@
         <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>1.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.5</v>
+        <v>1.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>25</v>
+        <v>1.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>1.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="AW2" t="n">
-        <v>18.5</v>
+        <v>1.18</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>1.18</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>1.18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>1.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>19.5</v>
+        <v>1.18</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>22</v>
+        <v>1.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>1.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>16.5</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>1.13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2.54</v>
+        <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>1.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>760</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,201 +1890,783 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Fortaleza FC</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Internacional de Bogotá</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>2.3</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-04-01 03:35:09</t>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -763,164 +763,164 @@
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.18</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.18</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.18</v>
+        <v>27</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.18</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.13</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.18</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.18</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.18</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.18</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.18</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.18</v>
+        <v>38</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.18</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.18</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.18</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.18</v>
+        <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I5" t="n">
-        <v>60</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
-        <v>1.35</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.48</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>760</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.51</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.55</v>
+        <v>2.98</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
-        <v>1.53</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,19 +787,19 @@
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
         <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
         <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,72 +937,72 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Bangkok Utd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.31</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.01</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>1.37</v>
       </c>
       <c r="G5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
         <v>4.1</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.84</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.93</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>1.33</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.51</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>B93 Copenhagen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Hobro</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.98</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.35</v>
-      </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Hillerod Fodbold</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,33 +2489,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.14</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2533,140 +2533,2468 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tammeka Tartu</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tallinna FC Flora</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>840</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>910</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>1.01</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-04-01 07:50:57</t>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Romanian Liga II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bihor Oradea</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Corum Belediyespor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bandirmaspor</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bodrum Belediyesi Bodrumspor</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Umraniyespor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH113"/>
+  <dimension ref="A1:BH114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +769,7 @@
         <v>2.36</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -799,7 +799,7 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -966,7 +966,7 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1002,7 +1002,7 @@
         <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1023,7 +1023,7 @@
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
         <v>40</v>
@@ -1080,10 +1080,10 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
@@ -1092,19 +1092,19 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>14.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
@@ -1187,10 +1187,10 @@
         <v>1.17</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="R5" t="n">
         <v>1.51</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1659,10 +1659,10 @@
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="AX6" t="n">
         <v>5.8</v>
@@ -1671,32 +1671,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="BB6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="BF6" t="n">
         <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
         <v>1.35</v>
@@ -2130,7 +2130,7 @@
         <v>5.9</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
@@ -2196,7 +2196,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>34</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2241,10 +2241,10 @@
         <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
@@ -2253,10 +2253,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.26</v>
@@ -2417,7 +2417,7 @@
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>9.800000000000001</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2733,10 +2733,10 @@
         <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>2.32</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2745,7 +2745,7 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
         <v>1.42</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I13" t="n">
         <v>3.5</v>
@@ -2924,13 +2924,13 @@
         <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.58</v>
+        <v>1.71</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -2942,7 +2942,7 @@
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="G14" t="n">
         <v>2.22</v>
@@ -3094,13 +3094,13 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3118,7 +3118,7 @@
         <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.53</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>2.78</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I17" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3691,13 +3691,13 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
         <v>1.6</v>
@@ -3709,13 +3709,13 @@
         <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
         <v>1.45</v>
@@ -3730,19 +3730,19 @@
         <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
         <v>30</v>
@@ -3757,46 +3757,46 @@
         <v>48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.42</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>1.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.8</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.8</v>
+        <v>1.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>1.33</v>
       </c>
       <c r="AX17" t="n">
         <v>14</v>
@@ -3817,20 +3817,20 @@
         <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>1.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.38</v>
+        <v>1.31</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
@@ -3897,10 +3897,10 @@
         <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.16</v>
       </c>
       <c r="G19" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>2.66</v>
@@ -4097,16 +4097,16 @@
         <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4273,16 +4273,16 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="O20" t="n">
         <v>1.06</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R20" t="n">
         <v>2.08</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>840</v>
+        <v>990</v>
       </c>
       <c r="H23" t="n">
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>910</v>
+        <v>990</v>
       </c>
       <c r="J23" t="n">
         <v>1.03</v>
@@ -4864,7 +4864,7 @@
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
@@ -4873,10 +4873,10 @@
         <v>1.09</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>1.13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.27</v>
       </c>
       <c r="G26" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H26" t="n">
         <v>11</v>
@@ -5437,16 +5437,16 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="R26" t="n">
         <v>1.72</v>
@@ -5461,10 +5461,10 @@
         <v>1.92</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X26" t="n">
         <v>40</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5628,25 +5628,25 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.52</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="T27" t="n">
         <v>1.6</v>
@@ -5673,34 +5673,34 @@
         <v>80</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF27" t="n">
         <v>17.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>50</v>
       </c>
       <c r="AJ27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
         <v>34</v>
@@ -5709,10 +5709,10 @@
         <v>80</v>
       </c>
       <c r="AN27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP27" t="n">
         <v>16.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G29" t="n">
         <v>1.36</v>
@@ -6004,7 +6004,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J29" t="n">
         <v>5.7</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>2.24</v>
       </c>
       <c r="O30" t="n">
         <v>1.15</v>
@@ -6231,16 +6231,16 @@
         <v>2.06</v>
       </c>
       <c r="T30" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>6.8</v>
@@ -6786,7 +6786,7 @@
         <v>4.9</v>
       </c>
       <c r="K33" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6801,16 +6801,16 @@
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="R33" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S33" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="T33" t="n">
         <v>1.6</v>
@@ -6819,7 +6819,7 @@
         <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="W33" t="n">
         <v>1.17</v>
@@ -6843,22 +6843,22 @@
         <v>15</v>
       </c>
       <c r="AD33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH33" t="n">
         <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ33" t="n">
         <v>160</v>
@@ -6873,10 +6873,10 @@
         <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO33" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AP33" t="n">
         <v>1.03</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
         <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G35" t="n">
         <v>1.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>1.31</v>
@@ -7464,59 +7464,59 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7789,10 +7789,10 @@
         <v>2.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7959,13 +7959,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O39" t="n">
         <v>1.28</v>
       </c>
       <c r="P39" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Q39" t="n">
         <v>1.28</v>
@@ -7974,7 +7974,7 @@
         <v>1.08</v>
       </c>
       <c r="S39" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G40" t="n">
         <v>2.94</v>
@@ -8159,7 +8159,7 @@
         <v>1.21</v>
       </c>
       <c r="P40" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
         <v>1.63</v>
@@ -8177,7 +8177,7 @@
         <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W40" t="n">
         <v>1.51</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -8553,16 +8553,16 @@
         <v>1.72</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S42" t="n">
         <v>1.72</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
         <v>1.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K43" t="n">
         <v>950</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="O44" t="n">
         <v>1.29</v>
@@ -8947,10 +8947,10 @@
         <v>2.84</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.18</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -9123,19 +9123,19 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O45" t="n">
         <v>1.24</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="R45" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
         <v>2.76</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>1.77</v>
       </c>
       <c r="G46" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>4.5</v>
@@ -9401,16 +9401,16 @@
         <v>95</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AQ46" t="n">
         <v>11.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AT46" t="n">
         <v>5.9</v>
@@ -9422,7 +9422,7 @@
         <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX46" t="n">
         <v>7.6</v>
@@ -9434,7 +9434,7 @@
         <v>12</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB46" t="n">
         <v>13</v>
@@ -9443,20 +9443,20 @@
         <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BF46" t="n">
         <v>7.8</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
         <v>1.73</v>
       </c>
       <c r="S47" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="T47" t="n">
         <v>1.84</v>
@@ -9556,7 +9556,7 @@
         <v>13</v>
       </c>
       <c r="AC47" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AD47" t="n">
         <v>38</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>2.34</v>
       </c>
       <c r="G48" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I48" t="n">
         <v>3.75</v>
       </c>
       <c r="J48" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K48" t="n">
         <v>3.5</v>
@@ -9702,10 +9702,10 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N48" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O48" t="n">
         <v>1.41</v>
@@ -9717,7 +9717,7 @@
         <v>2.12</v>
       </c>
       <c r="R48" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S48" t="n">
         <v>3.6</v>
@@ -9732,7 +9732,7 @@
         <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -9875,46 +9875,46 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G49" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I49" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="K49" t="n">
         <v>950</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="O49" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.49</v>
+        <v>2.74</v>
       </c>
       <c r="R49" t="n">
         <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>1.49</v>
+        <v>2.74</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -9923,10 +9923,10 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>1.8</v>
       </c>
       <c r="G50" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H50" t="n">
         <v>5</v>
@@ -10081,7 +10081,7 @@
         <v>6.4</v>
       </c>
       <c r="J50" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K50" t="n">
         <v>3.8</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -10287,7 +10287,7 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>1.27</v>
@@ -10302,7 +10302,7 @@
         <v>1.3</v>
       </c>
       <c r="S51" t="n">
-        <v>2.74</v>
+        <v>1.73</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="G52" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H52" t="n">
         <v>4.7</v>
@@ -10469,10 +10469,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K52" t="n">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10490,7 +10490,7 @@
         <v>2.06</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R52" t="n">
         <v>1.42</v>
@@ -10505,10 +10505,10 @@
         <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>2.24</v>
+        <v>1.59</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -10675,10 +10675,10 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O53" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P53" t="n">
         <v>1.62</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -10869,16 +10869,16 @@
         <v>1.04</v>
       </c>
       <c r="N54" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
         <v>1.21</v>
       </c>
       <c r="P54" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="R54" t="n">
         <v>1.37</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -11057,13 +11057,13 @@
         <v>4.9</v>
       </c>
       <c r="L55" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M55" t="n">
         <v>1.05</v>
       </c>
       <c r="N55" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O55" t="n">
         <v>1.25</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
         <v>2.72</v>
       </c>
       <c r="T56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U56" t="n">
         <v>1.01</v>
@@ -11341,52 +11341,52 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
         <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P57" t="n">
         <v>1.64</v>
@@ -11469,10 +11469,10 @@
         <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V57" t="n">
         <v>1.65</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -11806,31 +11806,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="G59" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H59" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>3.05</v>
       </c>
       <c r="K59" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -11839,22 +11839,22 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O59" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P59" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="R59" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S59" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T59" t="n">
         <v>1.11</v>
@@ -11863,10 +11863,10 @@
         <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W59" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -12000,55 +12000,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="G60" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H60" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S60" t="n">
         <v>3.25</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N60" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S60" t="n">
-        <v>4.3</v>
       </c>
       <c r="T60" t="n">
         <v>1.11</v>
@@ -12057,10 +12057,10 @@
         <v>1.11</v>
       </c>
       <c r="V60" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W60" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -12194,55 +12194,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="G61" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S61" t="n">
         <v>4.3</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J61" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3.1</v>
       </c>
       <c r="T61" t="n">
         <v>1.11</v>
@@ -12251,10 +12251,10 @@
         <v>1.11</v>
       </c>
       <c r="V61" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="W61" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -12388,67 +12388,67 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="G62" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="J62" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K62" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M62" t="n">
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O62" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="P62" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R62" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S62" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="W62" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,14 +12560,14 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12582,28 +12582,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Le Puy</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="G63" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="H63" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="K63" t="n">
         <v>950</v>
@@ -12615,34 +12615,34 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="O63" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P63" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="R63" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="T63" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W63" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -12702,49 +12702,49 @@
         <v>1.03</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF63" t="n">
         <v>1.01</v>
@@ -12754,14 +12754,14 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12776,31 +12776,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="G64" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="H64" t="n">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="K64" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,34 +12809,34 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="O64" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="P64" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="R64" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="T64" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U64" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V64" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W64" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12893,52 +12893,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -12948,14 +12948,14 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12970,186 +12970,186 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MVV Maastricht</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4.2</v>
+        <v>1.06</v>
       </c>
       <c r="G65" t="n">
-        <v>5.6</v>
+        <v>1.08</v>
       </c>
       <c r="H65" t="n">
-        <v>1.72</v>
+        <v>30</v>
       </c>
       <c r="I65" t="n">
-        <v>1.83</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="K65" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P65" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V65" t="n">
         <v>1.02</v>
       </c>
-      <c r="N65" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V65" t="n">
-        <v>2.2</v>
-      </c>
       <c r="W65" t="n">
-        <v>1.21</v>
+        <v>13.5</v>
       </c>
       <c r="X65" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="Y65" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="Z65" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AA65" t="n">
         <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC65" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AD65" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AE65" t="n">
         <v>1000</v>
       </c>
       <c r="AF65" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG65" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH65" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI65" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK65" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL65" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM65" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AN65" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="AO65" t="n">
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13164,179 +13164,179 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M66" t="n">
         <v>1.06</v>
       </c>
-      <c r="G66" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="H66" t="n">
+      <c r="N66" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG66" t="n">
         <v>30</v>
       </c>
-      <c r="I66" t="n">
-        <v>50</v>
-      </c>
-      <c r="J66" t="n">
-        <v>18</v>
-      </c>
-      <c r="K66" t="n">
-        <v>25</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N66" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P66" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R66" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W66" t="n">
-        <v>12</v>
-      </c>
-      <c r="X66" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>170</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>510</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>65</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>150</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>390</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>12</v>
-      </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -13358,179 +13358,179 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G67" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="H67" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J67" t="n">
         <v>3.55</v>
       </c>
-      <c r="I67" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J67" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K67" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L67" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M67" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N67" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="P67" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="R67" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T67" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="U67" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="V67" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W67" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="X67" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Y67" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z67" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA67" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB67" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD67" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE67" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AF67" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AG67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH67" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AI67" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AJ67" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK67" t="n">
         <v>24</v>
       </c>
       <c r="AL67" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD67" t="n">
         <v>36</v>
       </c>
-      <c r="AM67" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE67" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BF67" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG67" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -13552,179 +13552,179 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="G68" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="H68" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K68" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L68" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N68" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O68" t="n">
         <v>1.38</v>
       </c>
       <c r="P68" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R68" t="n">
         <v>1.27</v>
       </c>
       <c r="S68" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T68" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="U68" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W68" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="X68" t="n">
         <v>12.5</v>
       </c>
       <c r="Y68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD68" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z68" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AE68" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AF68" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG68" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH68" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI68" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AK68" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AL68" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM68" t="n">
         <v>140</v>
       </c>
       <c r="AN68" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AO68" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AP68" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV68" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ68" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU68" t="n">
+      <c r="AW68" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA68" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV68" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>50</v>
-      </c>
       <c r="BB68" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BC68" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BD68" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BE68" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF68" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BG68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -13746,179 +13746,179 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="G69" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N69" t="n">
         <v>3.05</v>
       </c>
-      <c r="H69" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J69" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K69" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O69" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P69" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R69" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S69" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T69" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W69" t="n">
         <v>1.98</v>
       </c>
-      <c r="V69" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X69" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AA69" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AB69" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AC69" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD69" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AE69" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AF69" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH69" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AI69" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ69" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AK69" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AL69" t="n">
         <v>55</v>
       </c>
       <c r="AM69" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AN69" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AO69" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AP69" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ69" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AS69" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT69" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AU69" t="n">
         <v>6.4</v>
       </c>
       <c r="AV69" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AW69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX69" t="n">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY69" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ69" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BA69" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BB69" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BC69" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BD69" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE69" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BF69" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BG69" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -13940,186 +13940,186 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="G70" t="n">
-        <v>2.02</v>
+        <v>2.76</v>
       </c>
       <c r="H70" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="J70" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K70" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N70" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P70" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q70" t="n">
         <v>2.2</v>
       </c>
       <c r="R70" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S70" t="n">
         <v>4.2</v>
       </c>
       <c r="T70" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U70" t="n">
         <v>2</v>
       </c>
-      <c r="U70" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V70" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="W70" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="X70" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y70" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ70" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z70" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU70" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV70" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW70" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX70" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY70" t="n">
+      <c r="BA70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE70" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ70" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA70" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB70" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC70" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD70" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE70" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF70" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BG70" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14134,179 +14134,179 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I71" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="K71" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N71" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="O71" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="P71" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="R71" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="S71" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="T71" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U71" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V71" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W71" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="X71" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y71" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z71" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA71" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB71" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC71" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD71" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE71" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF71" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG71" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH71" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI71" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ71" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK71" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL71" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM71" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN71" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO71" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ71" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR71" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS71" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT71" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU71" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV71" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW71" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX71" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY71" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ71" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA71" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB71" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC71" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD71" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE71" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF71" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG71" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -14328,28 +14328,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="G72" t="n">
-        <v>2.36</v>
+        <v>990</v>
       </c>
       <c r="H72" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
       <c r="K72" t="n">
         <v>950</v>
@@ -14358,25 +14358,25 @@
         <v>1.01</v>
       </c>
       <c r="M72" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N72" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="O72" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="P72" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q72" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R72" t="n">
         <v>1.42</v>
       </c>
-      <c r="R72" t="n">
-        <v>1.57</v>
-      </c>
       <c r="S72" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="T72" t="n">
         <v>1.11</v>
@@ -14385,10 +14385,10 @@
         <v>1.11</v>
       </c>
       <c r="V72" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W72" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -14522,55 +14522,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>MVV Maastricht</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="G73" t="n">
-        <v>2.74</v>
+        <v>5.3</v>
       </c>
       <c r="H73" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="J73" t="n">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="K73" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
       </c>
       <c r="M73" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N73" t="n">
-        <v>2.06</v>
+        <v>2.82</v>
       </c>
       <c r="O73" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P73" t="n">
-        <v>2.06</v>
+        <v>2.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="R73" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="S73" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="T73" t="n">
         <v>1.11</v>
@@ -14579,10 +14579,10 @@
         <v>1.11</v>
       </c>
       <c r="V73" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="W73" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14749,7 @@
         <v>1.03</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O74" t="n">
         <v>1.15</v>
@@ -14761,7 +14761,7 @@
         <v>1.54</v>
       </c>
       <c r="R74" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S74" t="n">
         <v>2.26</v>
@@ -14872,7 +14872,7 @@
         <v>4.3</v>
       </c>
       <c r="BC74" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD74" t="n">
         <v>20</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15113,19 +15113,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G76" t="n">
         <v>5.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="I76" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="J76" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="K76" t="n">
         <v>1000</v>
@@ -15137,7 +15137,7 @@
         <v>1.02</v>
       </c>
       <c r="N76" t="n">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="O76" t="n">
         <v>1.12</v>
@@ -15149,10 +15149,10 @@
         <v>1.4</v>
       </c>
       <c r="R76" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S76" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="T76" t="n">
         <v>1.11</v>
@@ -15161,7 +15161,7 @@
         <v>1.11</v>
       </c>
       <c r="V76" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W76" t="n">
         <v>1.24</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15501,19 +15501,19 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="G78" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="H78" t="n">
         <v>5.6</v>
       </c>
       <c r="I78" t="n">
-        <v>9.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J78" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K78" t="n">
         <v>8</v>
@@ -15525,13 +15525,13 @@
         <v>1.02</v>
       </c>
       <c r="N78" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="O78" t="n">
         <v>1.1</v>
       </c>
       <c r="P78" t="n">
-        <v>1.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q78" t="n">
         <v>1.1</v>
@@ -15540,19 +15540,19 @@
         <v>1.73</v>
       </c>
       <c r="S78" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="T78" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U78" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V78" t="n">
         <v>1.11</v>
       </c>
       <c r="W78" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15701,7 @@
         <v>3.3</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I79" t="n">
         <v>2.96</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -15901,7 +15901,7 @@
         <v>1000</v>
       </c>
       <c r="J80" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K80" t="n">
         <v>1000</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
         <v>1.56</v>
       </c>
       <c r="S82" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T82" t="n">
         <v>1.11</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
         <v>2.76</v>
       </c>
       <c r="T84" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U84" t="n">
         <v>2.18</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16850,55 +16850,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>LR Vicenza Virtus</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G85" t="n">
         <v>1000</v>
       </c>
       <c r="H85" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="J85" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K85" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L85" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M85" t="n">
         <v>1.01</v>
       </c>
       <c r="N85" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="O85" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P85" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.92</v>
+        <v>2.08</v>
       </c>
       <c r="R85" t="n">
         <v>1.18</v>
       </c>
       <c r="S85" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T85" t="n">
         <v>1.11</v>
@@ -16907,7 +16907,7 @@
         <v>1.11</v>
       </c>
       <c r="V85" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W85" t="n">
         <v>1.01</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -17044,109 +17044,109 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignanochiampo</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="G86" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="H86" t="n">
-        <v>4.7</v>
+        <v>2.86</v>
       </c>
       <c r="I86" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="J86" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="K86" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L86" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M86" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>2.58</v>
+        <v>1.98</v>
       </c>
       <c r="O86" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P86" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R86" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S86" t="n">
-        <v>4.8</v>
+        <v>2.74</v>
       </c>
       <c r="T86" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U86" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V86" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="W86" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="X86" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y86" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z86" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA86" t="n">
         <v>1000</v>
       </c>
       <c r="AB86" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC86" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD86" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE86" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF86" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG86" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH86" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI86" t="n">
         <v>1000</v>
       </c>
       <c r="AJ86" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK86" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL86" t="n">
         <v>1000</v>
@@ -17155,16 +17155,16 @@
         <v>1000</v>
       </c>
       <c r="AN86" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO86" t="n">
         <v>1000</v>
       </c>
       <c r="AP86" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ86" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR86" t="n">
         <v>1.03</v>
@@ -17173,34 +17173,34 @@
         <v>1.03</v>
       </c>
       <c r="AT86" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU86" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV86" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW86" t="n">
         <v>1.03</v>
       </c>
       <c r="AX86" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY86" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ86" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA86" t="n">
         <v>1.03</v>
       </c>
       <c r="BB86" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC86" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD86" t="n">
         <v>1.03</v>
@@ -17209,14 +17209,14 @@
         <v>1.03</v>
       </c>
       <c r="BF86" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG86" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -17238,179 +17238,179 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Arzignanochiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="G87" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K87" t="n">
         <v>3.3</v>
       </c>
-      <c r="H87" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K87" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L87" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M87" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N87" t="n">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="O87" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="P87" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="R87" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S87" t="n">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U87" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V87" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="W87" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="X87" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y87" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z87" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA87" t="n">
         <v>1000</v>
       </c>
       <c r="AB87" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC87" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD87" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE87" t="n">
         <v>1000</v>
       </c>
       <c r="AF87" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG87" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH87" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI87" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ87" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK87" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL87" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM87" t="n">
         <v>1000</v>
       </c>
       <c r="AN87" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO87" t="n">
         <v>1000</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU87" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV87" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW87" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX87" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY87" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ87" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA87" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB87" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC87" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD87" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE87" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF87" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG87" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -17432,67 +17432,67 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LR Vicenza Virtus</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="G88" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="I88" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="K88" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="L88" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M88" t="n">
         <v>1.01</v>
       </c>
       <c r="N88" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="O88" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P88" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="R88" t="n">
         <v>1.18</v>
       </c>
       <c r="S88" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T88" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U88" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V88" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="W88" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X88" t="n">
         <v>1000</v>
@@ -17604,14 +17604,14 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17626,186 +17626,186 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Admira Wacker</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F89" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I89" t="n">
+        <v>6</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K89" t="n">
+        <v>950</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP89" t="n">
         <v>2.62</v>
       </c>
-      <c r="G89" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H89" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J89" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>110</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S89" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T89" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W89" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP89" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ89" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AT89" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AU89" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AV89" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="AW89" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AX89" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AY89" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AZ89" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BA89" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BB89" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BC89" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BD89" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="BE89" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG89" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17820,55 +17820,55 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G90" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="H90" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J90" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="K90" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="L90" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M90" t="n">
         <v>1.01</v>
       </c>
       <c r="N90" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="O90" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P90" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.08</v>
+        <v>2.92</v>
       </c>
       <c r="R90" t="n">
         <v>1.18</v>
       </c>
       <c r="S90" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="T90" t="n">
         <v>1.11</v>
@@ -17877,10 +17877,10 @@
         <v>1.11</v>
       </c>
       <c r="V90" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W90" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -17992,14 +17992,14 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18014,67 +18014,67 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Admira Wacker</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="G91" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="H91" t="n">
-        <v>3.75</v>
+        <v>2.32</v>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="J91" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K91" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
       </c>
       <c r="M91" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="O91" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="P91" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R91" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S91" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T91" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U91" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V91" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="W91" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="X91" t="n">
         <v>1000</v>
@@ -18092,7 +18092,7 @@
         <v>1000</v>
       </c>
       <c r="AC91" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD91" t="n">
         <v>1000</v>
@@ -18101,7 +18101,7 @@
         <v>1000</v>
       </c>
       <c r="AF91" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG91" t="n">
         <v>1000</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -18208,55 +18208,55 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="G92" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="H92" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="I92" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J92" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="L92" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="M92" t="n">
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="O92" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P92" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="R92" t="n">
         <v>1.18</v>
       </c>
       <c r="S92" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T92" t="n">
         <v>1.11</v>
@@ -18265,10 +18265,10 @@
         <v>1.11</v>
       </c>
       <c r="V92" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W92" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G93" t="n">
         <v>2</v>
@@ -18435,16 +18435,16 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O93" t="n">
         <v>1.36</v>
       </c>
       <c r="P93" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
         <v>1.22</v>
@@ -18456,7 +18456,7 @@
         <v>1.67</v>
       </c>
       <c r="U93" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V93" t="n">
         <v>1.25</v>
@@ -18498,7 +18498,7 @@
         <v>29</v>
       </c>
       <c r="AI93" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ93" t="n">
         <v>30</v>
@@ -18519,62 +18519,62 @@
         <v>1000</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AQ93" t="n">
         <v>9.6</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AS93" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AU93" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AV93" t="n">
         <v>12.5</v>
       </c>
       <c r="AW93" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AX93" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AY93" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AZ93" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BA93" t="n">
         <v>2.88</v>
       </c>
       <c r="BB93" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BD93" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BE93" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BF93" t="n">
         <v>10.5</v>
       </c>
       <c r="BG93" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18629,7 @@
         <v>1.05</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O94" t="n">
         <v>1.26</v>
@@ -18713,52 +18713,52 @@
         <v>1000</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE94" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF94" t="n">
         <v>1.01</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -18823,13 +18823,13 @@
         <v>1.07</v>
       </c>
       <c r="N95" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="O95" t="n">
         <v>1.37</v>
       </c>
       <c r="P95" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q95" t="n">
         <v>1.98</v>
@@ -18910,49 +18910,49 @@
         <v>2.3</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AR95" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AS95" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AU95" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AV95" t="n">
         <v>2</v>
       </c>
       <c r="AW95" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AX95" t="n">
         <v>22</v>
       </c>
       <c r="AY95" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AZ95" t="n">
         <v>2.14</v>
       </c>
       <c r="BA95" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BB95" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BC95" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BD95" t="n">
         <v>2.3</v>
       </c>
       <c r="BE95" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BF95" t="n">
         <v>2.3</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
         <v>12.5</v>
       </c>
       <c r="BD101" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE101" t="n">
         <v>16</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
         <v>1.01</v>
       </c>
       <c r="N102" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="O102" t="n">
         <v>1.31</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20357,7 +20357,7 @@
         <v>4.4</v>
       </c>
       <c r="H103" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I103" t="n">
         <v>2.46</v>
@@ -20375,13 +20375,13 @@
         <v>1.01</v>
       </c>
       <c r="N103" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="O103" t="n">
         <v>1.35</v>
       </c>
       <c r="P103" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q103" t="n">
         <v>1.94</v>
@@ -20459,52 +20459,52 @@
         <v>1000</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE103" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF103" t="n">
         <v>1.01</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20554,7 +20554,7 @@
         <v>5.2</v>
       </c>
       <c r="I104" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J104" t="n">
         <v>3.85</v>
@@ -20569,7 +20569,7 @@
         <v>1.08</v>
       </c>
       <c r="N104" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>1.35</v>
@@ -20578,13 +20578,13 @@
         <v>1.9</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R104" t="n">
         <v>1.34</v>
       </c>
       <c r="S104" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T104" t="n">
         <v>1.95</v>
@@ -20593,10 +20593,10 @@
         <v>1.98</v>
       </c>
       <c r="V104" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X104" t="n">
         <v>13</v>
@@ -20623,7 +20623,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG104" t="n">
         <v>10.5</v>
@@ -20683,16 +20683,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ104" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA104" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB104" t="n">
         <v>17.5</v>
       </c>
       <c r="BC104" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD104" t="n">
         <v>34</v>
@@ -20704,11 +20704,11 @@
         <v>11.5</v>
       </c>
       <c r="BG104" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20769,7 +20769,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q105" t="n">
         <v>1.83</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -20960,7 +20960,7 @@
         <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P106" t="n">
         <v>1.47</v>
@@ -20969,10 +20969,10 @@
         <v>2.28</v>
       </c>
       <c r="R106" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S106" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="T106" t="n">
         <v>1.11</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -21515,46 +21515,46 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="G109" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H109" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="I109" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J109" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="K109" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="L109" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M109" t="n">
         <v>1.01</v>
       </c>
       <c r="N109" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O109" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P109" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R109" t="n">
         <v>1.18</v>
       </c>
       <c r="S109" t="n">
-        <v>2.88</v>
+        <v>1.4</v>
       </c>
       <c r="T109" t="n">
         <v>1.01</v>
@@ -21563,10 +21563,10 @@
         <v>1.01</v>
       </c>
       <c r="V109" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W109" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X109" t="n">
         <v>1000</v>
@@ -21623,52 +21623,52 @@
         <v>1000</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE109" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF109" t="n">
         <v>1.01</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G111" t="n">
         <v>2.56</v>
@@ -21912,25 +21912,25 @@
         <v>3.4</v>
       </c>
       <c r="I111" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J111" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K111" t="n">
         <v>3.5</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P111" t="n">
         <v>1.65</v>
@@ -21939,134 +21939,134 @@
         <v>2.3</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI111" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK111" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL111" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN111" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO111" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP111" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR111" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS111" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU111" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AV111" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW111" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX111" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY111" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BA111" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BB111" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC111" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BD111" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BE111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BF111" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG111" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -22112,19 +22112,19 @@
         <v>4.1</v>
       </c>
       <c r="K112" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P112" t="n">
         <v>1.83</v>
@@ -22133,141 +22133,141 @@
         <v>1.9</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE112" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22282,16 +22282,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="G113" t="n">
         <v>1000</v>
@@ -22303,158 +22303,352 @@
         <v>1000</v>
       </c>
       <c r="J113" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K113" t="n">
         <v>950</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P113" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP113" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR113" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS113" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV113" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX113" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY113" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ113" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA113" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB113" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BC113" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD113" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE113" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K114" t="n">
+        <v>950</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W114" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -763,10 +763,10 @@
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -790,7 +790,7 @@
         <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
@@ -799,19 +799,19 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
@@ -859,7 +859,7 @@
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
@@ -877,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.6</v>
@@ -910,7 +910,7 @@
         <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
         <v>16.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1014,7 +1014,7 @@
         <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
         <v>13.5</v>
@@ -1059,62 +1059,62 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
         <v>12</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AR3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AZ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
         <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>990</v>
@@ -1354,7 +1354,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I6" t="n">
         <v>12.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1584,7 +1584,7 @@
         <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1611,10 +1611,10 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1635,22 +1635,22 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1659,10 +1659,10 @@
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AX6" t="n">
         <v>5.8</v>
@@ -1671,32 +1671,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BB6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BF6" t="n">
         <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="J7" t="n">
         <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1757,16 +1757,16 @@
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,7 +1775,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I9" t="n">
         <v>13.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2157,7 +2157,7 @@
         <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
         <v>1.84</v>
@@ -2166,7 +2166,7 @@
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2181,7 +2181,7 @@
         <v>520</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
         <v>16.5</v>
@@ -2199,7 +2199,7 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI9" t="n">
         <v>170</v>
@@ -2211,7 +2211,7 @@
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>180</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2241,10 +2241,10 @@
         <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
@@ -2253,10 +2253,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
         <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.26</v>
@@ -2342,7 +2342,7 @@
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
         <v>1.43</v>
@@ -2360,7 +2360,7 @@
         <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
         <v>3.35</v>
@@ -2706,13 +2706,13 @@
         <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2727,16 +2727,16 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
         <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G13" t="n">
         <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2909,7 +2909,7 @@
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
@@ -2924,13 +2924,13 @@
         <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>1.71</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -2939,7 +2939,7 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
         <v>1.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>4.3</v>
@@ -3115,16 +3115,16 @@
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
         <v>1.48</v>
@@ -3133,10 +3133,10 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3205,13 +3205,13 @@
         <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW14" t="n">
         <v>3.85</v>
@@ -3220,7 +3220,7 @@
         <v>3.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AZ14" t="n">
         <v>3.45</v>
@@ -3241,14 +3241,14 @@
         <v>4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG14" t="n">
         <v>3.75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>2.24</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I16" t="n">
         <v>4.4</v>
@@ -3488,7 +3488,7 @@
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.32</v>
@@ -3497,13 +3497,13 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
         <v>1.98</v>
@@ -3521,10 +3521,10 @@
         <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
         <v>2.36</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3691,13 +3691,13 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
         <v>1.6</v>
@@ -3706,19 +3706,19 @@
         <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U17" t="n">
         <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3730,19 +3730,19 @@
         <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
         <v>30</v>
@@ -3763,40 +3763,40 @@
         <v>44</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
         <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>2.44</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.33</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
         <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.33</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>5.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
         <v>14</v>
@@ -3817,20 +3817,20 @@
         <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.33</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.33</v>
+        <v>2.22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>2.42</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4055,46 +4055,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
         <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
         <v>1.89</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -4103,7 +4103,7 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
         <v>1.66</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4273,19 +4273,19 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.06</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
         <v>1.43</v>
@@ -4300,7 +4300,7 @@
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
         <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H24" t="n">
         <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>4.5</v>
@@ -5049,10 +5049,10 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
         <v>2.72</v>
@@ -5061,13 +5061,13 @@
         <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S24" t="n">
         <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.42</v>
@@ -5076,119 +5076,119 @@
         <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y24" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="Z24" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV24" t="n">
         <v>16</v>
       </c>
-      <c r="AD24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>14</v>
-      </c>
       <c r="AW24" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ24" t="n">
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5225,40 +5225,40 @@
         <v>2.08</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5270,7 +5270,7 @@
         <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5285,10 +5285,10 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5297,10 +5297,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5321,68 +5321,68 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>16.5</v>
       </c>
       <c r="J26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>7.2</v>
@@ -5437,31 +5437,31 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
         <v>1.72</v>
       </c>
       <c r="S26" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="T26" t="n">
         <v>1.86</v>
       </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
         <v>3.9</v>
@@ -5470,7 +5470,7 @@
         <v>40</v>
       </c>
       <c r="Y26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5503,10 +5503,10 @@
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>40</v>
@@ -5521,16 +5521,16 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
         <v>8.800000000000001</v>
@@ -5539,10 +5539,10 @@
         <v>11</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
         <v>7.2</v>
@@ -5554,7 +5554,7 @@
         <v>19.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
@@ -5563,20 +5563,20 @@
         <v>10</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF26" t="n">
         <v>3.05</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.92</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H27" t="n">
         <v>3.65</v>
@@ -5619,7 +5619,7 @@
         <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
         <v>4.4</v>
@@ -5628,25 +5628,25 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.54</v>
       </c>
       <c r="T27" t="n">
         <v>1.6</v>
@@ -5658,7 +5658,7 @@
         <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X27" t="n">
         <v>26</v>
@@ -5670,7 +5670,7 @@
         <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB27" t="n">
         <v>13</v>
@@ -5706,7 +5706,7 @@
         <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN27" t="n">
         <v>11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G28" t="n">
         <v>3.15</v>
@@ -5816,40 +5816,40 @@
         <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
       </c>
       <c r="U28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
         <v>1.46</v>
@@ -5870,7 +5870,7 @@
         <v>17.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
         <v>14.5</v>
@@ -5903,7 +5903,7 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
         <v>21</v>
@@ -5918,7 +5918,7 @@
         <v>13</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5942,16 +5942,16 @@
         <v>11.5</v>
       </c>
       <c r="BA28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC28" t="n">
         <v>3.8</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BD28" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.85</v>
       </c>
       <c r="BE28" t="n">
         <v>4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.32</v>
       </c>
       <c r="G29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H29" t="n">
         <v>9.800000000000001</v>
@@ -6007,7 +6007,7 @@
         <v>12.5</v>
       </c>
       <c r="J29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K29" t="n">
         <v>7</v>
@@ -6019,28 +6019,28 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R29" t="n">
         <v>1.67</v>
       </c>
       <c r="S29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V29" t="n">
         <v>1.08</v>
@@ -6052,7 +6052,7 @@
         <v>38</v>
       </c>
       <c r="Y29" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z29" t="n">
         <v>130</v>
@@ -6064,7 +6064,7 @@
         <v>14</v>
       </c>
       <c r="AC29" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD29" t="n">
         <v>48</v>
@@ -6085,7 +6085,7 @@
         <v>140</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
         <v>17</v>
@@ -6097,22 +6097,22 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT29" t="n">
         <v>8.4</v>
@@ -6121,10 +6121,10 @@
         <v>10.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX29" t="n">
         <v>7.2</v>
@@ -6136,7 +6136,7 @@
         <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
         <v>8.199999999999999</v>
@@ -6145,20 +6145,20 @@
         <v>10</v>
       </c>
       <c r="BD29" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="G30" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H30" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6225,13 +6225,13 @@
         <v>1.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U30" t="n">
         <v>1.11</v>
@@ -6240,7 +6240,7 @@
         <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="G31" t="n">
         <v>1.47</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
         <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6601,25 +6601,25 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O32" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.38</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.48</v>
       </c>
       <c r="S32" t="n">
         <v>2.08</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U32" t="n">
         <v>1.11</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6801,13 +6801,13 @@
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q33" t="n">
         <v>1.43</v>
       </c>
       <c r="R33" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S33" t="n">
         <v>2.08</v>
@@ -6816,7 +6816,7 @@
         <v>1.6</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V33" t="n">
         <v>2.76</v>
@@ -6828,7 +6828,7 @@
         <v>40</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
         <v>15</v>
@@ -6852,13 +6852,13 @@
         <v>65</v>
       </c>
       <c r="AG33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ33" t="n">
         <v>160</v>
@@ -6870,13 +6870,13 @@
         <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN33" t="n">
         <v>55</v>
       </c>
       <c r="AO33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AP33" t="n">
         <v>1.03</v>
@@ -6885,16 +6885,16 @@
         <v>10.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS33" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV33" t="n">
         <v>8.199999999999999</v>
@@ -6906,10 +6906,10 @@
         <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA33" t="n">
         <v>18.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="G34" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="H34" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,34 +6989,34 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O34" t="n">
         <v>1.12</v>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
         <v>1.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W34" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>10.5</v>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J35" t="n">
         <v>5.2</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7353,25 +7353,25 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G36" t="n">
         <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
         <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
@@ -7383,7 +7383,7 @@
         <v>1.31</v>
       </c>
       <c r="P36" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q36" t="n">
         <v>1.78</v>
@@ -7407,7 +7407,7 @@
         <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7744,10 +7744,10 @@
         <v>2.04</v>
       </c>
       <c r="G38" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I38" t="n">
         <v>4.2</v>
@@ -7756,7 +7756,7 @@
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7792,7 +7792,7 @@
         <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
         <v>6.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BC40" t="n">
         <v>6.2</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G41" t="n">
         <v>1.6</v>
@@ -8338,10 +8338,10 @@
         <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8517,46 +8517,46 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="G42" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="H42" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="I42" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M42" t="n">
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.89</v>
+        <v>2.78</v>
       </c>
       <c r="O42" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="T42" t="n">
         <v>1.11</v>
@@ -8565,10 +8565,10 @@
         <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8711,46 +8711,46 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J43" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M43" t="n">
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P43" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S43" t="n">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="T43" t="n">
         <v>1.11</v>
@@ -8759,10 +8759,10 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -8908,43 +8908,43 @@
         <v>1.68</v>
       </c>
       <c r="G44" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H44" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I44" t="n">
         <v>6.4</v>
       </c>
       <c r="J44" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K44" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="O44" t="n">
         <v>1.29</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -8953,10 +8953,10 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W44" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
         <v>1.9</v>
       </c>
       <c r="I45" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J45" t="n">
         <v>3.7</v>
@@ -9123,34 +9123,34 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
         <v>1.24</v>
       </c>
       <c r="P45" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="Q45" t="n">
         <v>1.65</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S45" t="n">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="T45" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W45" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>1.77</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H46" t="n">
         <v>4.5</v>
@@ -9305,7 +9305,7 @@
         <v>5.9</v>
       </c>
       <c r="J46" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K46" t="n">
         <v>4.3</v>
@@ -9314,10 +9314,10 @@
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>2.94</v>
+        <v>1.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.29</v>
@@ -9335,16 +9335,16 @@
         <v>2.74</v>
       </c>
       <c r="T46" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U46" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V46" t="n">
         <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -9520,13 +9520,13 @@
         <v>2.82</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R47" t="n">
         <v>1.73</v>
       </c>
       <c r="S47" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="T47" t="n">
         <v>1.84</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="G48" t="n">
         <v>2.52</v>
       </c>
       <c r="H48" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I48" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>500</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9711,10 +9711,10 @@
         <v>1.41</v>
       </c>
       <c r="P48" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R48" t="n">
         <v>1.19</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G49" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H49" t="n">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="K49" t="n">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L49" t="n">
         <v>1.58</v>
@@ -9899,34 +9899,34 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="O49" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="P49" t="n">
         <v>1.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R49" t="n">
         <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W49" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G51" t="n">
         <v>1.79</v>
@@ -10275,25 +10275,25 @@
         <v>9.6</v>
       </c>
       <c r="J51" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K51" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M51" t="n">
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="O51" t="n">
         <v>1.27</v>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q51" t="n">
         <v>1.73</v>
@@ -10302,7 +10302,7 @@
         <v>1.3</v>
       </c>
       <c r="S51" t="n">
-        <v>1.73</v>
+        <v>2.74</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -10314,7 +10314,7 @@
         <v>1.11</v>
       </c>
       <c r="W51" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="G52" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="H52" t="n">
         <v>4.7</v>
@@ -10472,7 +10472,7 @@
         <v>3.85</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10493,7 +10493,7 @@
         <v>1.54</v>
       </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
         <v>2.28</v>
@@ -10505,10 +10505,10 @@
         <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W52" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -10651,40 +10651,40 @@
         </is>
       </c>
       <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K53" t="n">
         <v>4.7</v>
       </c>
-      <c r="G53" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L53" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M53" t="n">
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="O53" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="P53" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R53" t="n">
         <v>1.19</v>
@@ -10699,10 +10699,10 @@
         <v>1.11</v>
       </c>
       <c r="V53" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="W53" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G54" t="n">
         <v>1.73</v>
       </c>
       <c r="H54" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I54" t="n">
         <v>8.800000000000001</v>
@@ -10860,7 +10860,7 @@
         <v>3.75</v>
       </c>
       <c r="K54" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10869,16 +10869,16 @@
         <v>1.04</v>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O54" t="n">
         <v>1.21</v>
       </c>
       <c r="P54" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="R54" t="n">
         <v>1.37</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -11039,28 +11039,28 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G55" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="H55" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K55" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M55" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N55" t="n">
         <v>4.1</v>
@@ -11090,119 +11090,119 @@
         <v>1.13</v>
       </c>
       <c r="W55" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="X55" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z55" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC55" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AD55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH55" t="n">
         <v>32</v>
       </c>
-      <c r="AE55" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>27</v>
-      </c>
       <c r="AI55" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL55" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM55" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AO55" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>13.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ55" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="AT55" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AU55" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="AX55" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY55" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ55" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="BB55" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.95</v>
+        <v>2.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="BF55" t="n">
-        <v>6</v>
+        <v>1.98</v>
       </c>
       <c r="BG55" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G56" t="n">
         <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I56" t="n">
         <v>2.2</v>
@@ -11248,7 +11248,7 @@
         <v>2.64</v>
       </c>
       <c r="K56" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L56" t="n">
         <v>1.35</v>
@@ -11257,28 +11257,28 @@
         <v>1.05</v>
       </c>
       <c r="N56" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O56" t="n">
         <v>1.26</v>
       </c>
       <c r="P56" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R56" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S56" t="n">
         <v>2.72</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V56" t="n">
         <v>1.83</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -11427,25 +11427,25 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G57" t="n">
         <v>4.9</v>
       </c>
       <c r="H57" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I57" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="K57" t="n">
         <v>3.6</v>
       </c>
       <c r="L57" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
@@ -11454,13 +11454,13 @@
         <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P57" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R57" t="n">
         <v>1.19</v>
@@ -11475,7 +11475,7 @@
         <v>1.11</v>
       </c>
       <c r="V57" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="W57" t="n">
         <v>1.25</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -11621,43 +11621,43 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G58" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H58" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J58" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K58" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L58" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M58" t="n">
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="R58" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S58" t="n">
         <v>3.15</v>
@@ -11669,10 +11669,10 @@
         <v>1.11</v>
       </c>
       <c r="V58" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W58" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -11815,13 +11815,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="G59" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H59" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="I59" t="n">
         <v>3.5</v>
@@ -11830,7 +11830,7 @@
         <v>3.05</v>
       </c>
       <c r="K59" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -11848,10 +11848,10 @@
         <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S59" t="n">
         <v>3.35</v>
@@ -11866,7 +11866,7 @@
         <v>1.4</v>
       </c>
       <c r="W59" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12009,25 +12009,25 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G60" t="n">
         <v>3.4</v>
       </c>
       <c r="H60" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
@@ -12039,13 +12039,13 @@
         <v>1.34</v>
       </c>
       <c r="P60" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R60" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S60" t="n">
         <v>3.25</v>
@@ -12057,7 +12057,7 @@
         <v>1.11</v>
       </c>
       <c r="V60" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W60" t="n">
         <v>1.42</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12203,19 +12203,19 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G61" t="n">
         <v>3.15</v>
       </c>
       <c r="H61" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K61" t="n">
         <v>3.25</v>
@@ -12227,16 +12227,16 @@
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O61" t="n">
         <v>1.09</v>
       </c>
       <c r="P61" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="R61" t="n">
         <v>1.18</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12397,13 +12397,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G62" t="n">
         <v>4.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I62" t="n">
         <v>2.52</v>
@@ -12421,7 +12421,7 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O62" t="n">
         <v>1.31</v>
@@ -12430,10 +12430,10 @@
         <v>1.84</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R62" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S62" t="n">
         <v>3.1</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12591,25 +12591,25 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G63" t="n">
         <v>3.4</v>
       </c>
       <c r="H63" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K63" t="n">
         <v>950</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
@@ -12621,25 +12621,25 @@
         <v>1.41</v>
       </c>
       <c r="P63" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q63" t="n">
         <v>2.06</v>
       </c>
       <c r="R63" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S63" t="n">
         <v>3.6</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V63" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W63" t="n">
         <v>1.42</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G64" t="n">
         <v>2.58</v>
       </c>
       <c r="H64" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I64" t="n">
         <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="K64" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12824,13 +12824,13 @@
         <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T64" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U64" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V64" t="n">
         <v>1.25</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -12988,13 +12988,13 @@
         <v>30</v>
       </c>
       <c r="I65" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J65" t="n">
         <v>21</v>
       </c>
       <c r="K65" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13033,7 +13033,7 @@
         <v>13.5</v>
       </c>
       <c r="X65" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Y65" t="n">
         <v>170</v>
@@ -13048,7 +13048,7 @@
         <v>21</v>
       </c>
       <c r="AC65" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AD65" t="n">
         <v>150</v>
@@ -13063,7 +13063,7 @@
         <v>19</v>
       </c>
       <c r="AH65" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AI65" t="n">
         <v>390</v>
@@ -13078,37 +13078,37 @@
         <v>50</v>
       </c>
       <c r="AM65" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AO65" t="n">
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR65" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT65" t="n">
         <v>17</v>
       </c>
       <c r="AU65" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW65" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX65" t="n">
         <v>10</v>
@@ -13117,32 +13117,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA65" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB65" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC65" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD65" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE65" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BG65" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -13173,13 +13173,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G66" t="n">
         <v>2.3</v>
       </c>
       <c r="H66" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I66" t="n">
         <v>3.85</v>
@@ -13221,7 +13221,7 @@
         <v>2.22</v>
       </c>
       <c r="V66" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W66" t="n">
         <v>1.77</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -13367,22 +13367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="G67" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="H67" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J67" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K67" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L67" t="n">
         <v>1.4</v>
@@ -13391,61 +13391,61 @@
         <v>1.08</v>
       </c>
       <c r="N67" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O67" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P67" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R67" t="n">
         <v>1.27</v>
       </c>
       <c r="S67" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U67" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V67" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W67" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="X67" t="n">
         <v>12.5</v>
       </c>
       <c r="Y67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF67" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>12</v>
       </c>
       <c r="AG67" t="n">
         <v>11</v>
@@ -13457,80 +13457,80 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK67" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL67" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM67" t="n">
         <v>140</v>
       </c>
       <c r="AN67" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AO67" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP67" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR67" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AS67" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY67" t="n">
         <v>10</v>
       </c>
-      <c r="AT67" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX67" t="n">
+      <c r="AZ67" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE67" t="n">
         <v>10</v>
       </c>
-      <c r="AY67" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF67" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BG67" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G69" t="n">
         <v>2.02</v>
@@ -13770,7 +13770,7 @@
         <v>3.55</v>
       </c>
       <c r="K69" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13788,7 +13788,7 @@
         <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R69" t="n">
         <v>1.26</v>
@@ -13815,13 +13815,13 @@
         <v>15.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA69" t="n">
         <v>130</v>
       </c>
       <c r="AB69" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC69" t="n">
         <v>9.4</v>
@@ -13842,7 +13842,7 @@
         <v>27</v>
       </c>
       <c r="AI69" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ69" t="n">
         <v>27</v>
@@ -13869,22 +13869,22 @@
         <v>10</v>
       </c>
       <c r="AR69" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT69" t="n">
         <v>6.6</v>
       </c>
       <c r="AU69" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV69" t="n">
         <v>16</v>
       </c>
       <c r="AW69" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX69" t="n">
         <v>9.800000000000001</v>
@@ -13896,7 +13896,7 @@
         <v>20</v>
       </c>
       <c r="BA69" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB69" t="n">
         <v>20</v>
@@ -13905,20 +13905,20 @@
         <v>18</v>
       </c>
       <c r="BD69" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF69" t="n">
         <v>14</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
         <v>4.2</v>
       </c>
       <c r="T70" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U70" t="n">
         <v>2</v>
@@ -14015,19 +14015,19 @@
         <v>55</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
       <c r="AD70" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE70" t="n">
         <v>40</v>
       </c>
       <c r="AF70" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG70" t="n">
         <v>12.5</v>
@@ -14078,7 +14078,7 @@
         <v>12</v>
       </c>
       <c r="AW70" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX70" t="n">
         <v>15</v>
@@ -14087,32 +14087,32 @@
         <v>11</v>
       </c>
       <c r="AZ70" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA70" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB70" t="n">
         <v>32</v>
       </c>
       <c r="BC70" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD70" t="n">
         <v>38</v>
       </c>
       <c r="BE70" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF70" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG70" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G71" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H71" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="K71" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14179,10 +14179,10 @@
         <v>1.42</v>
       </c>
       <c r="R71" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S71" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T71" t="n">
         <v>1.11</v>
@@ -14191,10 +14191,10 @@
         <v>1.11</v>
       </c>
       <c r="V71" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W71" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X71" t="n">
         <v>1000</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -14337,19 +14337,19 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="G72" t="n">
-        <v>990</v>
+        <v>2.84</v>
       </c>
       <c r="H72" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J72" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
         <v>950</v>
@@ -14361,22 +14361,22 @@
         <v>1.03</v>
       </c>
       <c r="N72" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="O72" t="n">
         <v>1.18</v>
       </c>
       <c r="P72" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R72" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S72" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T72" t="n">
         <v>1.11</v>
@@ -14385,10 +14385,10 @@
         <v>1.11</v>
       </c>
       <c r="V72" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W72" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
         <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="J73" t="n">
         <v>4.4</v>
@@ -14564,10 +14564,10 @@
         <v>2.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R73" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S73" t="n">
         <v>1.79</v>
@@ -14582,7 +14582,7 @@
         <v>2.2</v>
       </c>
       <c r="W73" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14749,7 @@
         <v>1.03</v>
       </c>
       <c r="N74" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O74" t="n">
         <v>1.15</v>
@@ -14761,16 +14761,16 @@
         <v>1.54</v>
       </c>
       <c r="R74" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S74" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="T74" t="n">
         <v>1.38</v>
       </c>
       <c r="U74" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V74" t="n">
         <v>1.39</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -14922,16 +14922,16 @@
         <v>1.44</v>
       </c>
       <c r="G75" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H75" t="n">
         <v>1.04</v>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>990</v>
       </c>
       <c r="J75" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="K75" t="n">
         <v>950</v>
@@ -14958,7 +14958,7 @@
         <v>1.9</v>
       </c>
       <c r="S75" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T75" t="n">
         <v>1.11</v>
@@ -14967,10 +14967,10 @@
         <v>1.11</v>
       </c>
       <c r="V75" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W75" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -15113,19 +15113,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G76" t="n">
         <v>5.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I76" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="J76" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="K76" t="n">
         <v>1000</v>
@@ -15137,22 +15137,22 @@
         <v>1.02</v>
       </c>
       <c r="N76" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>1.12</v>
       </c>
       <c r="P76" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R76" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S76" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="T76" t="n">
         <v>1.11</v>
@@ -15161,10 +15161,10 @@
         <v>1.11</v>
       </c>
       <c r="V76" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="W76" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="G77" t="n">
         <v>1.23</v>
@@ -15319,7 +15319,7 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="K77" t="n">
         <v>13</v>
@@ -15340,7 +15340,7 @@
         <v>3</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R77" t="n">
         <v>1.87</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G78" t="n">
         <v>1.63</v>
@@ -15510,10 +15510,10 @@
         <v>5.6</v>
       </c>
       <c r="I78" t="n">
-        <v>990</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K78" t="n">
         <v>8</v>
@@ -15525,22 +15525,22 @@
         <v>1.02</v>
       </c>
       <c r="N78" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>1.1</v>
       </c>
       <c r="P78" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="R78" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S78" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="T78" t="n">
         <v>1.11</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -15698,16 +15698,16 @@
         <v>2.26</v>
       </c>
       <c r="G79" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H79" t="n">
         <v>2.08</v>
       </c>
       <c r="I79" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="J79" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="K79" t="n">
         <v>950</v>
@@ -15719,7 +15719,7 @@
         <v>1.02</v>
       </c>
       <c r="N79" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O79" t="n">
         <v>1.1</v>
@@ -15734,7 +15734,7 @@
         <v>1.72</v>
       </c>
       <c r="S79" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T79" t="n">
         <v>1.11</v>
@@ -15743,10 +15743,10 @@
         <v>1.11</v>
       </c>
       <c r="V79" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W79" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X79" t="n">
         <v>1000</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G80" t="n">
         <v>1000</v>
@@ -15898,10 +15898,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="K80" t="n">
         <v>1000</v>
@@ -15913,13 +15913,13 @@
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="O80" t="n">
         <v>1.01</v>
       </c>
       <c r="P80" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q80" t="n">
         <v>2.66</v>
@@ -15937,7 +15937,7 @@
         <v>1.11</v>
       </c>
       <c r="V80" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="W80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -16083,22 +16083,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="G81" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H81" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="I81" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="K81" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q81" t="n">
         <v>3.05</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -16280,10 +16280,10 @@
         <v>1.64</v>
       </c>
       <c r="G82" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="H82" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I82" t="n">
         <v>5.3</v>
@@ -16301,16 +16301,16 @@
         <v>1.03</v>
       </c>
       <c r="N82" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O82" t="n">
         <v>1.14</v>
       </c>
       <c r="P82" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R82" t="n">
         <v>1.56</v>
@@ -16328,7 +16328,7 @@
         <v>1.23</v>
       </c>
       <c r="W82" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
         <v>1.84</v>
       </c>
       <c r="I83" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J83" t="n">
         <v>4</v>
@@ -16510,7 +16510,7 @@
         <v>1.56</v>
       </c>
       <c r="S83" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T83" t="n">
         <v>1.56</v>
@@ -16519,7 +16519,7 @@
         <v>2.42</v>
       </c>
       <c r="V83" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W83" t="n">
         <v>1.3</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
         <v>4.3</v>
       </c>
       <c r="J84" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K84" t="n">
         <v>4.2</v>
@@ -16689,7 +16689,7 @@
         <v>1.05</v>
       </c>
       <c r="N84" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="O84" t="n">
         <v>1.25</v>
@@ -16701,13 +16701,13 @@
         <v>1.76</v>
       </c>
       <c r="R84" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S84" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="T84" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U84" t="n">
         <v>2.18</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -16862,22 +16862,22 @@
         <v>2.7</v>
       </c>
       <c r="G85" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H85" t="n">
         <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J85" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="K85" t="n">
         <v>7.6</v>
       </c>
       <c r="L85" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M85" t="n">
         <v>1.01</v>
@@ -16889,16 +16889,16 @@
         <v>1.02</v>
       </c>
       <c r="P85" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R85" t="n">
         <v>1.18</v>
       </c>
       <c r="S85" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T85" t="n">
         <v>1.11</v>
@@ -16907,10 +16907,10 @@
         <v>1.11</v>
       </c>
       <c r="V85" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W85" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X85" t="n">
         <v>1000</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -17053,22 +17053,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G86" t="n">
         <v>3.3</v>
       </c>
       <c r="H86" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="I86" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J86" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K86" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L86" t="n">
         <v>1.47</v>
@@ -17077,16 +17077,16 @@
         <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O86" t="n">
         <v>1.26</v>
       </c>
       <c r="P86" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R86" t="n">
         <v>1.18</v>
@@ -17101,7 +17101,7 @@
         <v>1.11</v>
       </c>
       <c r="V86" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W86" t="n">
         <v>1.43</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -17247,16 +17247,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G87" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H87" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J87" t="n">
         <v>2.94</v>
@@ -17265,16 +17265,16 @@
         <v>3.3</v>
       </c>
       <c r="L87" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M87" t="n">
         <v>1.12</v>
       </c>
       <c r="N87" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="O87" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="P87" t="n">
         <v>1.55</v>
@@ -17283,10 +17283,10 @@
         <v>2.52</v>
       </c>
       <c r="R87" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T87" t="n">
         <v>2.06</v>
@@ -17295,10 +17295,10 @@
         <v>1.76</v>
       </c>
       <c r="V87" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W87" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X87" t="n">
         <v>10</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -17441,37 +17441,37 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G88" t="n">
         <v>3.05</v>
       </c>
       <c r="H88" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I88" t="n">
         <v>4.5</v>
       </c>
       <c r="J88" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L88" t="n">
         <v>1.5</v>
       </c>
       <c r="M88" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="O88" t="n">
         <v>1.3</v>
       </c>
       <c r="P88" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Q88" t="n">
         <v>2.4</v>
@@ -17498,7 +17498,7 @@
         <v>1000</v>
       </c>
       <c r="Y88" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z88" t="n">
         <v>1000</v>
@@ -17507,10 +17507,10 @@
         <v>1000</v>
       </c>
       <c r="AB88" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC88" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD88" t="n">
         <v>1000</v>
@@ -17522,7 +17522,7 @@
         <v>1000</v>
       </c>
       <c r="AG88" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH88" t="n">
         <v>1000</v>
@@ -17549,62 +17549,62 @@
         <v>1000</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU88" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AV88" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ88" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA88" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BC88" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD88" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BG88" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -17641,34 +17641,34 @@
         <v>2.36</v>
       </c>
       <c r="H89" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I89" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J89" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K89" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L89" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M89" t="n">
         <v>1.08</v>
       </c>
       <c r="N89" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O89" t="n">
         <v>1.08</v>
       </c>
       <c r="P89" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R89" t="n">
         <v>1.18</v>
@@ -17686,7 +17686,7 @@
         <v>1.2</v>
       </c>
       <c r="W89" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X89" t="n">
         <v>1000</v>
@@ -17704,7 +17704,7 @@
         <v>1000</v>
       </c>
       <c r="AC89" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD89" t="n">
         <v>1000</v>
@@ -17743,62 +17743,62 @@
         <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR89" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD89" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS89" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW89" t="n">
+      <c r="BE89" t="n">
         <v>2.58</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE89" t="n">
-        <v>2.62</v>
       </c>
       <c r="BF89" t="n">
         <v>14</v>
       </c>
       <c r="BG89" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -17856,7 +17856,7 @@
         <v>1.25</v>
       </c>
       <c r="O90" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P90" t="n">
         <v>1.24</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -18026,37 +18026,37 @@
         <v>2.62</v>
       </c>
       <c r="G91" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H91" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I91" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="K91" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L91" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M91" t="n">
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O91" t="n">
         <v>1.39</v>
       </c>
       <c r="P91" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R91" t="n">
         <v>1.25</v>
@@ -18065,10 +18065,10 @@
         <v>3.15</v>
       </c>
       <c r="T91" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U91" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V91" t="n">
         <v>1.47</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
         <v>2.12</v>
       </c>
       <c r="G92" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H92" t="n">
         <v>2.4</v>
@@ -18229,10 +18229,10 @@
         <v>3.85</v>
       </c>
       <c r="J92" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K92" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L92" t="n">
         <v>1.38</v>
@@ -18241,22 +18241,22 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O92" t="n">
         <v>1.02</v>
       </c>
       <c r="P92" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R92" t="n">
         <v>1.18</v>
       </c>
       <c r="S92" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T92" t="n">
         <v>1.11</v>
@@ -18268,7 +18268,7 @@
         <v>1.35</v>
       </c>
       <c r="W92" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -18411,22 +18411,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="H93" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="J93" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K93" t="n">
-        <v>3.75</v>
+        <v>640</v>
       </c>
       <c r="L93" t="n">
         <v>1.01</v>
@@ -18435,25 +18435,25 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O93" t="n">
         <v>1.36</v>
       </c>
       <c r="P93" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q93" t="n">
         <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S93" t="n">
         <v>3.35</v>
       </c>
       <c r="T93" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U93" t="n">
         <v>1.65</v>
@@ -18462,7 +18462,7 @@
         <v>1.25</v>
       </c>
       <c r="W93" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="X93" t="n">
         <v>17</v>
@@ -18486,7 +18486,7 @@
         <v>28</v>
       </c>
       <c r="AE93" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF93" t="n">
         <v>15.5</v>
@@ -18507,74 +18507,74 @@
         <v>30</v>
       </c>
       <c r="AL93" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM93" t="n">
         <v>1000</v>
       </c>
       <c r="AN93" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO93" t="n">
         <v>1000</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AQ93" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AS93" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AU93" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AV93" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW93" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AX93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY93" t="n">
         <v>2.48</v>
       </c>
-      <c r="AY93" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AZ93" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BA93" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BB93" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BD93" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BE93" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BF93" t="n">
         <v>10.5</v>
       </c>
       <c r="BG93" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -18605,22 +18605,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="G94" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="H94" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K94" t="n">
-        <v>5.7</v>
+        <v>590</v>
       </c>
       <c r="L94" t="n">
         <v>1.01</v>
@@ -18635,10 +18635,10 @@
         <v>1.26</v>
       </c>
       <c r="P94" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="R94" t="n">
         <v>1.32</v>
@@ -18653,10 +18653,10 @@
         <v>1.11</v>
       </c>
       <c r="V94" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W94" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="X94" t="n">
         <v>1000</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -18805,13 +18805,13 @@
         <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I95" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J95" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K95" t="n">
         <v>3.85</v>
@@ -18820,7 +18820,7 @@
         <v>1.01</v>
       </c>
       <c r="M95" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N95" t="n">
         <v>3.55</v>
@@ -18829,7 +18829,7 @@
         <v>1.37</v>
       </c>
       <c r="P95" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q95" t="n">
         <v>1.98</v>
@@ -18841,19 +18841,19 @@
         <v>3.4</v>
       </c>
       <c r="T95" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U95" t="n">
         <v>1.64</v>
       </c>
-      <c r="U95" t="n">
-        <v>1.61</v>
-      </c>
       <c r="V95" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W95" t="n">
         <v>1.2</v>
       </c>
       <c r="X95" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y95" t="n">
         <v>11</v>
@@ -18910,59 +18910,59 @@
         <v>2.3</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AR95" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AS95" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AU95" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AV95" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AW95" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AX95" t="n">
-        <v>22</v>
+        <v>2.58</v>
       </c>
       <c r="AY95" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="AZ95" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="BA95" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="BB95" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="BC95" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="BD95" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="BE95" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="BF95" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="BG95" t="n">
         <v>10.5</v>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19008,16 +19008,16 @@
         <v>3.05</v>
       </c>
       <c r="K96" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L96" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M96" t="n">
         <v>1.01</v>
       </c>
       <c r="N96" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O96" t="n">
         <v>1.39</v>
@@ -19029,7 +19029,7 @@
         <v>2.02</v>
       </c>
       <c r="R96" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S96" t="n">
         <v>3.55</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19208,25 +19208,25 @@
         <v>1.01</v>
       </c>
       <c r="M97" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N97" t="n">
-        <v>4.3</v>
+        <v>2.24</v>
       </c>
       <c r="O97" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P97" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="R97" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S97" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="T97" t="n">
         <v>1.9</v>
@@ -19295,7 +19295,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ97" t="n">
         <v>7.8</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
         <v>3.1</v>
       </c>
       <c r="H98" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I98" t="n">
         <v>3.55</v>
@@ -19396,10 +19396,10 @@
         <v>3.25</v>
       </c>
       <c r="K98" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L98" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M98" t="n">
         <v>1.01</v>
@@ -19414,13 +19414,13 @@
         <v>1.84</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R98" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S98" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T98" t="n">
         <v>1.11</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19575,13 +19575,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="G99" t="n">
         <v>32</v>
       </c>
       <c r="H99" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I99" t="n">
         <v>1.54</v>
@@ -19590,16 +19590,16 @@
         <v>4.3</v>
       </c>
       <c r="K99" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="L99" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M99" t="n">
         <v>1.01</v>
       </c>
       <c r="N99" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O99" t="n">
         <v>1.26</v>
@@ -19611,16 +19611,16 @@
         <v>1.65</v>
       </c>
       <c r="R99" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S99" t="n">
         <v>2.1</v>
       </c>
       <c r="T99" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U99" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V99" t="n">
         <v>2.84</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19772,22 +19772,22 @@
         <v>1.94</v>
       </c>
       <c r="G100" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H100" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>3.05</v>
       </c>
       <c r="K100" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L100" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M100" t="n">
         <v>1.01</v>
@@ -19802,19 +19802,19 @@
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R100" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S100" t="n">
         <v>3.2</v>
       </c>
       <c r="T100" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U100" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V100" t="n">
         <v>1.25</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -19981,7 +19981,7 @@
         <v>6.4</v>
       </c>
       <c r="L101" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M101" t="n">
         <v>1.03</v>
@@ -19993,7 +19993,7 @@
         <v>1.2</v>
       </c>
       <c r="P101" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q101" t="n">
         <v>1.61</v>
@@ -20050,7 +20050,7 @@
         <v>30</v>
       </c>
       <c r="AI101" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ101" t="n">
         <v>10.5</v>
@@ -20065,7 +20065,7 @@
         <v>170</v>
       </c>
       <c r="AN101" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO101" t="n">
         <v>230</v>
@@ -20077,13 +20077,13 @@
         <v>32</v>
       </c>
       <c r="AR101" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS101" t="n">
         <v>15.5</v>
       </c>
       <c r="AT101" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU101" t="n">
         <v>12</v>
@@ -20092,7 +20092,7 @@
         <v>36</v>
       </c>
       <c r="AW101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX101" t="n">
         <v>7.6</v>
@@ -20104,7 +20104,7 @@
         <v>25</v>
       </c>
       <c r="BA101" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB101" t="n">
         <v>9.199999999999999</v>
@@ -20116,17 +20116,17 @@
         <v>32</v>
       </c>
       <c r="BE101" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF101" t="n">
         <v>4.3</v>
       </c>
       <c r="BG101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -20157,13 +20157,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G102" t="n">
         <v>3.2</v>
       </c>
       <c r="H102" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I102" t="n">
         <v>3.2</v>
@@ -20172,28 +20172,28 @@
         <v>3.25</v>
       </c>
       <c r="K102" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L102" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M102" t="n">
         <v>1.01</v>
       </c>
       <c r="N102" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="O102" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P102" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q102" t="n">
         <v>1.81</v>
       </c>
       <c r="R102" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S102" t="n">
         <v>3</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -20357,16 +20357,16 @@
         <v>4.4</v>
       </c>
       <c r="H103" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I103" t="n">
         <v>2.46</v>
       </c>
       <c r="J103" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K103" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L103" t="n">
         <v>1.01</v>
@@ -20381,22 +20381,22 @@
         <v>1.35</v>
       </c>
       <c r="P103" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R103" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S103" t="n">
         <v>3.25</v>
       </c>
       <c r="T103" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U103" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V103" t="n">
         <v>1.68</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -20548,16 +20548,16 @@
         <v>1.81</v>
       </c>
       <c r="G104" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H104" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I104" t="n">
         <v>5.4</v>
       </c>
       <c r="J104" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K104" t="n">
         <v>3.9</v>
@@ -20590,13 +20590,13 @@
         <v>1.95</v>
       </c>
       <c r="U104" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X104" t="n">
         <v>13</v>
@@ -20689,7 +20689,7 @@
         <v>65</v>
       </c>
       <c r="BB104" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC104" t="n">
         <v>18</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20739,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G105" t="n">
         <v>1.3</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -20933,25 +20933,25 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G106" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H106" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>2.9</v>
       </c>
       <c r="K106" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L106" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M106" t="n">
         <v>1.01</v>
@@ -20963,16 +20963,16 @@
         <v>1.02</v>
       </c>
       <c r="P106" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R106" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S106" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T106" t="n">
         <v>1.11</v>
@@ -20981,7 +20981,7 @@
         <v>1.11</v>
       </c>
       <c r="V106" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="W106" t="n">
         <v>1.48</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -21515,37 +21515,37 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G109" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H109" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="I109" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J109" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K109" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L109" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M109" t="n">
         <v>1.01</v>
       </c>
       <c r="N109" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="O109" t="n">
         <v>1.02</v>
       </c>
       <c r="P109" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q109" t="n">
         <v>2.06</v>
@@ -21554,19 +21554,19 @@
         <v>1.18</v>
       </c>
       <c r="S109" t="n">
-        <v>1.4</v>
+        <v>2.96</v>
       </c>
       <c r="T109" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U109" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V109" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="W109" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X109" t="n">
         <v>1000</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -21742,7 +21742,7 @@
         <v>1.41</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -21906,13 +21906,13 @@
         <v>2.3</v>
       </c>
       <c r="G111" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H111" t="n">
         <v>3.4</v>
       </c>
       <c r="I111" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J111" t="n">
         <v>3.15</v>
@@ -21924,10 +21924,10 @@
         <v>1.01</v>
       </c>
       <c r="M111" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="O111" t="n">
         <v>1.45</v>
@@ -21939,134 +21939,134 @@
         <v>2.3</v>
       </c>
       <c r="R111" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S111" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T111" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U111" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V111" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W111" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X111" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF111" t="n">
         <v>15</v>
       </c>
-      <c r="Y111" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z111" t="n">
+      <c r="AG111" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN111" t="n">
         <v>32</v>
       </c>
-      <c r="AA111" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC111" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF111" t="n">
+      <c r="AO111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR111" t="n">
         <v>20</v>
       </c>
-      <c r="AG111" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AS111" t="n">
-        <v>2.98</v>
+        <v>7.2</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="AU111" t="n">
-        <v>2.34</v>
+        <v>6.4</v>
       </c>
       <c r="AV111" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="AW111" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="AX111" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AY111" t="n">
-        <v>2.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ111" t="n">
-        <v>2.78</v>
+        <v>5.9</v>
       </c>
       <c r="BA111" t="n">
-        <v>2.98</v>
+        <v>7</v>
       </c>
       <c r="BB111" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BC111" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BD111" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="BE111" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="BF111" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG111" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -22097,22 +22097,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G112" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H112" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I112" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="J112" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K112" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L112" t="n">
         <v>1.01</v>
@@ -22121,34 +22121,34 @@
         <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>1.24</v>
+        <v>2.94</v>
       </c>
       <c r="O112" t="n">
         <v>1.28</v>
       </c>
       <c r="P112" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q112" t="n">
         <v>1.9</v>
       </c>
       <c r="R112" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S112" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="T112" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U112" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V112" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W112" t="n">
-        <v>1.6</v>
+        <v>2.74</v>
       </c>
       <c r="X112" t="n">
         <v>1000</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
         <v>1.17</v>
       </c>
       <c r="G113" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H113" t="n">
         <v>1.04</v>
@@ -22303,19 +22303,19 @@
         <v>1000</v>
       </c>
       <c r="J113" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K113" t="n">
         <v>950</v>
       </c>
       <c r="L113" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M113" t="n">
         <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O113" t="n">
         <v>1.15</v>
@@ -22330,19 +22330,19 @@
         <v>1.25</v>
       </c>
       <c r="S113" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T113" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U113" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V113" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W113" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X113" t="n">
         <v>1000</v>
@@ -22399,52 +22399,52 @@
         <v>1000</v>
       </c>
       <c r="AP113" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ113" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR113" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AS113" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT113" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU113" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV113" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW113" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX113" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY113" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ113" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA113" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB113" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC113" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD113" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE113" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF113" t="n">
         <v>1.01</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -22485,31 +22485,31 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="G114" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H114" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I114" t="n">
         <v>4.6</v>
       </c>
       <c r="J114" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="K114" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L114" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M114" t="n">
         <v>1.01</v>
       </c>
       <c r="N114" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="O114" t="n">
         <v>1.35</v>
@@ -22524,19 +22524,19 @@
         <v>1.18</v>
       </c>
       <c r="S114" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="T114" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U114" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V114" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="W114" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="X114" t="n">
         <v>1000</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH114"/>
+  <dimension ref="A1:BH116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
         <v>2.38</v>
@@ -772,10 +772,10 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -799,16 +799,16 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -817,7 +817,7 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>32</v>
@@ -832,7 +832,7 @@
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
         <v>26</v>
@@ -859,7 +859,7 @@
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
@@ -1065,7 +1065,7 @@
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS3" t="n">
         <v>4.9</v>
@@ -1089,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
@@ -1098,7 +1098,7 @@
         <v>4.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
         <v>4.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1635,22 +1635,22 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AT6" t="n">
         <v>5.4</v>
@@ -1659,10 +1659,10 @@
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AX6" t="n">
         <v>5.8</v>
@@ -1671,32 +1671,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BB6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.18</v>
+        <v>9.6</v>
       </c>
       <c r="BD6" t="n">
         <v>2.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BF6" t="n">
         <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
         <v>1.33</v>
@@ -2139,28 +2139,28 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
         <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.08</v>
@@ -2169,13 +2169,13 @@
         <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
         <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>520</v>
@@ -2184,79 +2184,79 @@
         <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AE9" t="n">
         <v>220</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
         <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AR9" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.2</v>
+        <v>95</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
         <v>9.199999999999999</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="BF9" t="n">
         <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
         <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2450,16 +2450,16 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
         <v>4.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G11" t="n">
         <v>2.14</v>
@@ -2512,13 +2512,13 @@
         <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2736,7 +2736,7 @@
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>2.32</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2745,7 +2745,7 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
         <v>1.42</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2939,7 +2939,7 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
         <v>1.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I14" t="n">
         <v>3.9</v>
@@ -3100,7 +3100,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.65</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>3.35</v>
       </c>
       <c r="H17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3709,7 +3709,7 @@
         <v>2.46</v>
       </c>
       <c r="T17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>2.3</v>
@@ -3718,7 +3718,7 @@
         <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3826,11 +3826,11 @@
         <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
         <v>2.36</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J21" t="n">
         <v>1.04</v>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="G24" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J24" t="n">
         <v>6</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,146 +5049,146 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="Z24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG24" t="n">
         <v>14</v>
       </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU24" t="n">
         <v>11</v>
       </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5327,16 +5327,16 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ25" t="n">
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
         <v>6.6</v>
@@ -5348,7 +5348,7 @@
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AX25" t="n">
         <v>7.8</v>
@@ -5360,7 +5360,7 @@
         <v>11.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BB25" t="n">
         <v>12.5</v>
@@ -5369,20 +5369,20 @@
         <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BF25" t="n">
         <v>6.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="G26" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>16.5</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,146 +5437,146 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="X26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y26" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM26" t="n">
         <v>65</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AN26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT26" t="n">
         <v>11.5</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
         <v>16</v>
       </c>
-      <c r="AL26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="AW26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX26" t="n">
         <v>11</v>
       </c>
-      <c r="AV26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5616,13 +5616,13 @@
         <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5652,10 +5652,10 @@
         <v>1.6</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
         <v>1.98</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT27" t="n">
         <v>9.4</v>
@@ -5736,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
@@ -5748,7 +5748,7 @@
         <v>12</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB27" t="n">
         <v>18</v>
@@ -5760,17 +5760,17 @@
         <v>21</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF27" t="n">
         <v>8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>2.76</v>
       </c>
       <c r="G28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H28" t="n">
         <v>2.36</v>
       </c>
       <c r="I28" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -5834,13 +5834,13 @@
         <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5888,7 +5888,7 @@
         <v>19</v>
       </c>
       <c r="AI28" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
         <v>55</v>
@@ -5897,7 +5897,7 @@
         <v>38</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>13</v>
       </c>
-      <c r="AS28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA28" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.95</v>
+        <v>32</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BG28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
         <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X29" t="n">
         <v>38</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G30" t="n">
         <v>2.6</v>
@@ -6198,13 +6198,13 @@
         <v>2.88</v>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>85</v>
+        <v>8.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6228,7 +6228,7 @@
         <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T30" t="n">
         <v>1.44</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>1.36</v>
       </c>
       <c r="G31" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K31" t="n">
         <v>6.2</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
         <v>5.1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>10.5</v>
@@ -6891,7 +6891,7 @@
         <v>13.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU33" t="n">
         <v>11</v>
@@ -6903,10 +6903,10 @@
         <v>11</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AZ33" t="n">
         <v>16</v>
@@ -6915,26 +6915,26 @@
         <v>18.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG33" t="n">
         <v>4.1</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7168,13 +7168,13 @@
         <v>10.5</v>
       </c>
       <c r="I35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J35" t="n">
         <v>5.2</v>
       </c>
       <c r="K35" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>2.04</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H38" t="n">
         <v>3.25</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
         <v>4.9</v>
@@ -7765,34 +7765,34 @@
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R38" t="n">
         <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U38" t="n">
         <v>2.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7873,10 +7873,10 @@
         <v>4.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ38" t="n">
         <v>3.95</v>
@@ -7897,14 +7897,14 @@
         <v>4.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG38" t="n">
         <v>4.4</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8138,13 +8138,13 @@
         <v>2.48</v>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J40" t="n">
         <v>3.6</v>
       </c>
       <c r="K40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8156,19 +8156,19 @@
         <v>4.6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P40" t="n">
         <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R40" t="n">
         <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
         <v>1.57</v>
@@ -8183,7 +8183,7 @@
         <v>1.51</v>
       </c>
       <c r="X40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y40" t="n">
         <v>15.5</v>
@@ -8192,7 +8192,7 @@
         <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB40" t="n">
         <v>18</v>
@@ -8246,7 +8246,7 @@
         <v>16.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="AT40" t="n">
         <v>12.5</v>
@@ -8270,10 +8270,10 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
         <v>6.2</v>
@@ -8282,7 +8282,7 @@
         <v>6.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF40" t="n">
         <v>15</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8517,37 +8517,37 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H42" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M42" t="n">
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>1.1</v>
       </c>
       <c r="O42" t="n">
         <v>1.29</v>
       </c>
       <c r="P42" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
         <v>1.58</v>
@@ -8556,7 +8556,7 @@
         <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T42" t="n">
         <v>1.11</v>
@@ -8565,10 +8565,10 @@
         <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W42" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H43" t="n">
         <v>2.16</v>
@@ -8726,7 +8726,7 @@
         <v>2.84</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L43" t="n">
         <v>1.29</v>
@@ -8735,22 +8735,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="R43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T43" t="n">
         <v>1.11</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G44" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H44" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I44" t="n">
         <v>6.4</v>
@@ -8920,7 +8920,7 @@
         <v>3.45</v>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L44" t="n">
         <v>1.3</v>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O44" t="n">
         <v>1.29</v>
@@ -8938,7 +8938,7 @@
         <v>1.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R44" t="n">
         <v>1.3</v>
@@ -8956,7 +8956,7 @@
         <v>1.19</v>
       </c>
       <c r="W44" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I45" t="n">
         <v>2.04</v>
@@ -9210,7 +9210,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR45" t="n">
         <v>9.6</v>
@@ -9231,7 +9231,7 @@
         <v>14.5</v>
       </c>
       <c r="AX45" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY45" t="n">
         <v>12.5</v>
@@ -9240,7 +9240,7 @@
         <v>12.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB45" t="n">
         <v>4</v>
@@ -9249,7 +9249,7 @@
         <v>3.95</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE45" t="n">
         <v>4</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>1.77</v>
       </c>
       <c r="G46" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H46" t="n">
         <v>4.5</v>
@@ -9317,7 +9317,7 @@
         <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>1.1</v>
+        <v>2.94</v>
       </c>
       <c r="O46" t="n">
         <v>1.29</v>
@@ -9335,16 +9335,16 @@
         <v>2.74</v>
       </c>
       <c r="T46" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="U46" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
         <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9365,7 +9365,7 @@
         <v>12.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE46" t="n">
         <v>90</v>
@@ -9395,7 +9395,7 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO46" t="n">
         <v>95</v>
@@ -9410,10 +9410,10 @@
         <v>2.44</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AT46" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU46" t="n">
         <v>5.8</v>
@@ -9446,17 +9446,17 @@
         <v>2.44</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BF46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG46" t="n">
         <v>2.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
         <v>2.42</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
         <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>2.78</v>
+        <v>1.05</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -10642,55 +10642,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="G53" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="H53" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="I53" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K53" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L53" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M53" t="n">
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="O53" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P53" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R53" t="n">
         <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T53" t="n">
         <v>1.11</v>
@@ -10699,10 +10699,10 @@
         <v>1.11</v>
       </c>
       <c r="V53" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>1.51</v>
       </c>
       <c r="G55" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H55" t="n">
         <v>5.3</v>
@@ -11069,7 +11069,7 @@
         <v>1.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
         <v>1.75</v>
@@ -11084,13 +11084,13 @@
         <v>1.84</v>
       </c>
       <c r="U55" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V55" t="n">
         <v>1.13</v>
       </c>
       <c r="W55" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
         <v>1.11</v>
       </c>
       <c r="V56" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W56" t="n">
         <v>1.22</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11418,55 +11418,55 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="H57" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="J57" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K57" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="L57" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.02</v>
       </c>
       <c r="P57" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R57" t="n">
         <v>1.19</v>
       </c>
       <c r="S57" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T57" t="n">
         <v>1.11</v>
@@ -11475,10 +11475,10 @@
         <v>1.11</v>
       </c>
       <c r="V57" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="W57" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -11806,55 +11806,55 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="G59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H59" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K59" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="L59" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M59" t="n">
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P59" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R59" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S59" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T59" t="n">
         <v>1.11</v>
@@ -11863,10 +11863,10 @@
         <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W59" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -12000,55 +12000,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="G60" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="K60" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="L60" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="O60" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="P60" t="n">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="R60" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S60" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T60" t="n">
         <v>1.11</v>
@@ -12057,10 +12057,10 @@
         <v>1.11</v>
       </c>
       <c r="V60" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="W60" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -12194,55 +12194,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="G61" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="H61" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="J61" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="K61" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L61" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="M61" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="O61" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="P61" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="R61" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S61" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="T61" t="n">
         <v>1.11</v>
@@ -12251,10 +12251,10 @@
         <v>1.11</v>
       </c>
       <c r="V61" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="W61" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -12388,55 +12388,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="G62" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="H62" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="I62" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K62" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L62" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M62" t="n">
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="O62" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="P62" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R62" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S62" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T62" t="n">
         <v>1.11</v>
@@ -12445,10 +12445,10 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="W62" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,14 +12560,14 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12582,67 +12582,67 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Puy</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="G63" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="H63" t="n">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>2.9</v>
       </c>
       <c r="K63" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L63" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O63" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P63" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R63" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S63" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T63" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U63" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V63" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="W63" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -12699,52 +12699,52 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF63" t="n">
         <v>1.01</v>
@@ -12754,14 +12754,14 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12776,31 +12776,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="G64" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="H64" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,34 +12809,34 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="O64" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="P64" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S64" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="T64" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U64" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V64" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W64" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12893,52 +12893,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -12948,14 +12948,14 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12970,186 +12970,186 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.06</v>
+        <v>1.65</v>
       </c>
       <c r="G65" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="H65" t="n">
-        <v>30</v>
+        <v>3.8</v>
       </c>
       <c r="I65" t="n">
-        <v>46</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="K65" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N65" t="n">
-        <v>11.5</v>
+        <v>2.32</v>
       </c>
       <c r="O65" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="P65" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="R65" t="n">
-        <v>2.58</v>
+        <v>1.56</v>
       </c>
       <c r="S65" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="T65" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U65" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V65" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="W65" t="n">
-        <v>13.5</v>
+        <v>1.98</v>
       </c>
       <c r="X65" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="Y65" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="Z65" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AA65" t="n">
         <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC65" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AD65" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AE65" t="n">
         <v>1000</v>
       </c>
       <c r="AF65" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG65" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH65" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AI65" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AJ65" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK65" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL65" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM65" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="AO65" t="n">
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR65" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS65" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT65" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU65" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW65" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX65" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY65" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA65" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB65" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC65" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD65" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE65" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG65" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13164,179 +13164,179 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.16</v>
+        <v>1.06</v>
       </c>
       <c r="G66" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="H66" t="n">
-        <v>3.45</v>
+        <v>30</v>
       </c>
       <c r="I66" t="n">
-        <v>3.85</v>
+        <v>46</v>
       </c>
       <c r="J66" t="n">
-        <v>3.45</v>
+        <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>3.7</v>
+        <v>29</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
       </c>
       <c r="M66" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="O66" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="P66" t="n">
-        <v>2.02</v>
+        <v>4.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="R66" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>1.52</v>
       </c>
       <c r="T66" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="U66" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="V66" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="W66" t="n">
-        <v>1.77</v>
+        <v>12</v>
       </c>
       <c r="X66" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>510</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>150</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG66" t="n">
         <v>19</v>
       </c>
-      <c r="Y66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB66" t="n">
+      <c r="AH66" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP66" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC66" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF66" t="n">
+      <c r="AQ66" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY66" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ66" t="n">
+      <c r="AZ66" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA66" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV66" t="n">
+      <c r="BB66" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE66" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW66" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>7</v>
-      </c>
       <c r="BF66" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="BG66" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -13358,179 +13358,179 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G67" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H67" t="n">
         <v>3.45</v>
       </c>
       <c r="I67" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>3.45</v>
       </c>
       <c r="K67" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L67" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N67" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="O67" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="P67" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="R67" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="U67" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="V67" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W67" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X67" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y67" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Z67" t="n">
         <v>28</v>
       </c>
       <c r="AA67" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB67" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AC67" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD67" t="n">
         <v>16</v>
       </c>
       <c r="AE67" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF67" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH67" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AI67" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AJ67" t="n">
         <v>29</v>
       </c>
       <c r="AK67" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL67" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM67" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AN67" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AO67" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AP67" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AS67" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AT67" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU67" t="n">
         <v>7</v>
       </c>
       <c r="AV67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ67" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW67" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>18</v>
-      </c>
       <c r="BA67" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BB67" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BC67" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD67" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BF67" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BG67" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -13552,179 +13552,179 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="G68" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N68" t="n">
         <v>3.05</v>
       </c>
-      <c r="H68" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I68" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K68" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N68" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O68" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P68" t="n">
         <v>1.73</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R68" t="n">
         <v>1.27</v>
       </c>
       <c r="S68" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="V68" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W68" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="X68" t="n">
         <v>12.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AA68" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL68" t="n">
         <v>48</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>55</v>
       </c>
       <c r="AM68" t="n">
         <v>140</v>
       </c>
       <c r="AN68" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AO68" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AP68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE68" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ68" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF68" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BG68" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -13746,179 +13746,179 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="G69" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="H69" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="I69" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K69" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S69" t="n">
         <v>3.95</v>
       </c>
-      <c r="L69" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S69" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T69" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U69" t="n">
         <v>2</v>
       </c>
-      <c r="U69" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V69" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="W69" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="X69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD69" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y69" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z69" t="n">
+      <c r="AE69" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK69" t="n">
         <v>38</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>27</v>
       </c>
       <c r="AL69" t="n">
         <v>55</v>
       </c>
       <c r="AM69" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AN69" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AO69" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AP69" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ69" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR69" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT69" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU69" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX69" t="n">
         <v>16</v>
       </c>
-      <c r="AW69" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX69" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY69" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ69" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BB69" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BC69" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BD69" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF69" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -13940,186 +13940,186 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="G70" t="n">
-        <v>2.76</v>
+        <v>2.02</v>
       </c>
       <c r="H70" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N70" t="n">
         <v>3</v>
       </c>
-      <c r="I70" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J70" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K70" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L70" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N70" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O70" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P70" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R70" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S70" t="n">
         <v>4.2</v>
       </c>
       <c r="T70" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="V70" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W70" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="X70" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y70" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Z70" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD70" t="n">
         <v>21</v>
       </c>
-      <c r="AA70" t="n">
+      <c r="AE70" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL70" t="n">
         <v>55</v>
       </c>
-      <c r="AB70" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>50</v>
-      </c>
       <c r="AM70" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AN70" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AO70" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AP70" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ70" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR70" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="AS70" t="n">
-        <v>42</v>
+        <v>5.3</v>
       </c>
       <c r="AT70" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AU70" t="n">
         <v>6.6</v>
       </c>
       <c r="AV70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW70" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AX70" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY70" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA70" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BB70" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BC70" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BD70" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="BE70" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF70" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BG70" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14134,179 +14134,179 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.77</v>
+        <v>2.52</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="H71" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="J71" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="K71" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N71" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="O71" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="P71" t="n">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="R71" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="S71" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="T71" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U71" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V71" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="W71" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="X71" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB71" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC71" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD71" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE71" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF71" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG71" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH71" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI71" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ71" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK71" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL71" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM71" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN71" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO71" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW71" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX71" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY71" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA71" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB71" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC71" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD71" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE71" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF71" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG71" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -14328,28 +14328,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G72" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="H72" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I72" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="K72" t="n">
         <v>950</v>
@@ -14358,25 +14358,25 @@
         <v>1.01</v>
       </c>
       <c r="M72" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N72" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O72" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P72" t="n">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="R72" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S72" t="n">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="T72" t="n">
         <v>1.11</v>
@@ -14385,10 +14385,10 @@
         <v>1.11</v>
       </c>
       <c r="V72" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -14522,55 +14522,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MVV Maastricht</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="G73" t="n">
-        <v>5.3</v>
+        <v>2.82</v>
       </c>
       <c r="H73" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="I73" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="J73" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
       </c>
       <c r="M73" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N73" t="n">
-        <v>2.82</v>
+        <v>1.1</v>
       </c>
       <c r="O73" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="P73" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="R73" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="S73" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="T73" t="n">
         <v>1.11</v>
@@ -14579,10 +14579,10 @@
         <v>1.11</v>
       </c>
       <c r="V73" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="W73" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -14758,13 +14758,13 @@
         <v>2.56</v>
       </c>
       <c r="Q74" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R74" t="n">
         <v>1.54</v>
       </c>
-      <c r="R74" t="n">
-        <v>1.61</v>
-      </c>
       <c r="S74" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T74" t="n">
         <v>1.38</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
         <v>1.87</v>
       </c>
       <c r="S77" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T77" t="n">
         <v>1.11</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15704,10 +15704,10 @@
         <v>2.08</v>
       </c>
       <c r="I79" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="K79" t="n">
         <v>950</v>
@@ -15743,7 +15743,7 @@
         <v>1.11</v>
       </c>
       <c r="V79" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W79" t="n">
         <v>1.45</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
         <v>1000</v>
       </c>
       <c r="H80" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I80" t="n">
         <v>2.2</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -16268,55 +16268,55 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>MVV Maastricht</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.64</v>
+        <v>4.2</v>
       </c>
       <c r="G82" t="n">
-        <v>2.02</v>
+        <v>5.3</v>
       </c>
       <c r="H82" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>1.83</v>
       </c>
       <c r="J82" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K82" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
       </c>
       <c r="M82" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N82" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="O82" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P82" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R82" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="S82" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="T82" t="n">
         <v>1.11</v>
@@ -16325,11 +16325,11 @@
         <v>1.11</v>
       </c>
       <c r="V82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W82" t="n">
         <v>1.23</v>
       </c>
-      <c r="W82" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X82" t="n">
         <v>1000</v>
       </c>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -16462,179 +16462,179 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="G83" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I83" t="n">
         <v>4.3</v>
       </c>
-      <c r="H83" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I83" t="n">
-        <v>2.02</v>
-      </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K83" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L83" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M83" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N83" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="O83" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P83" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="R83" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="S83" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="T83" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="U83" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="V83" t="n">
-        <v>1.98</v>
+        <v>1.3</v>
       </c>
       <c r="W83" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="X83" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y83" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="Z83" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB83" t="n">
         <v>18</v>
       </c>
-      <c r="AA83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO83" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP83" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR83" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS83" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT83" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU83" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV83" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW83" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX83" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY83" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ83" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB83" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC83" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BD83" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE83" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF83" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BG83" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -16656,179 +16656,179 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Neuchatel Xamax</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="G84" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="H84" t="n">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>2.02</v>
       </c>
       <c r="J84" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K84" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S84" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB84" t="n">
         <v>4.2</v>
       </c>
-      <c r="L84" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P84" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S84" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U84" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V84" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X84" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU84" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>18</v>
-      </c>
       <c r="BC84" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD84" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE84" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF84" t="n">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BG84" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -16850,179 +16850,179 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LR Vicenza Virtus</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="G85" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="I85" t="n">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="J85" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="K85" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="L85" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N85" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O85" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P85" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R85" t="n">
         <v>1.18</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T85" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U85" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V85" t="n">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="W85" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="X85" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y85" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z85" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA85" t="n">
         <v>1000</v>
       </c>
       <c r="AB85" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC85" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD85" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE85" t="n">
         <v>1000</v>
       </c>
       <c r="AF85" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG85" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH85" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI85" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK85" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL85" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM85" t="n">
         <v>1000</v>
       </c>
       <c r="AN85" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO85" t="n">
         <v>1000</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU85" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV85" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW85" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX85" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY85" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ85" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA85" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB85" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC85" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD85" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE85" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF85" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG85" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -17044,55 +17044,55 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Arzignanochiampo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="G86" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="H86" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="I86" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="J86" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="K86" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L86" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M86" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N86" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="O86" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="P86" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R86" t="n">
         <v>1.18</v>
       </c>
       <c r="S86" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T86" t="n">
         <v>1.11</v>
@@ -17101,10 +17101,10 @@
         <v>1.11</v>
       </c>
       <c r="V86" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W86" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="X86" t="n">
         <v>1000</v>
@@ -17131,7 +17131,7 @@
         <v>1000</v>
       </c>
       <c r="AF86" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG86" t="n">
         <v>1000</v>
@@ -17161,62 +17161,62 @@
         <v>1000</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AT86" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU86" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV86" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AX86" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY86" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ86" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA86" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BB86" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BC86" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BD86" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BE86" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BF86" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG86" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -17238,179 +17238,179 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignanochiampo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G87" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="H87" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="I87" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="K87" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L87" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M87" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N87" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="O87" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="P87" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="R87" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S87" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="T87" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U87" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V87" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="W87" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="X87" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y87" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z87" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA87" t="n">
         <v>1000</v>
       </c>
       <c r="AB87" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC87" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD87" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE87" t="n">
         <v>1000</v>
       </c>
       <c r="AF87" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG87" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH87" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI87" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ87" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK87" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL87" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM87" t="n">
         <v>1000</v>
       </c>
       <c r="AN87" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO87" t="n">
         <v>1000</v>
       </c>
       <c r="AP87" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ87" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR87" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS87" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT87" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU87" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV87" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW87" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX87" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY87" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ87" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA87" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB87" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC87" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD87" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE87" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF87" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG87" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -17432,55 +17432,55 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>LR Vicenza Virtus</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="G88" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="H88" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>2.64</v>
       </c>
       <c r="J88" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="K88" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="L88" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="M88" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N88" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="O88" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P88" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="R88" t="n">
         <v>1.18</v>
       </c>
       <c r="S88" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T88" t="n">
         <v>1.11</v>
@@ -17489,16 +17489,16 @@
         <v>1.11</v>
       </c>
       <c r="V88" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="W88" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="X88" t="n">
         <v>1000</v>
       </c>
       <c r="Y88" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z88" t="n">
         <v>1000</v>
@@ -17507,10 +17507,10 @@
         <v>1000</v>
       </c>
       <c r="AB88" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC88" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD88" t="n">
         <v>1000</v>
@@ -17522,7 +17522,7 @@
         <v>1000</v>
       </c>
       <c r="AG88" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH88" t="n">
         <v>1000</v>
@@ -17549,69 +17549,69 @@
         <v>1000</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ88" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR88" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS88" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT88" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AU88" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV88" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW88" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX88" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY88" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ88" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA88" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BB88" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="BD88" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE88" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BF88" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BG88" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17626,55 +17626,55 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="G89" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H89" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I89" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J89" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="K89" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L89" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M89" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N89" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="O89" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="P89" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="R89" t="n">
         <v>1.18</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T89" t="n">
         <v>1.11</v>
@@ -17683,10 +17683,10 @@
         <v>1.11</v>
       </c>
       <c r="V89" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W89" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X89" t="n">
         <v>1000</v>
@@ -17713,7 +17713,7 @@
         <v>1000</v>
       </c>
       <c r="AF89" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG89" t="n">
         <v>1000</v>
@@ -17743,69 +17743,69 @@
         <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="AQ89" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR89" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="AS89" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="AT89" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU89" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV89" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW89" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AX89" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY89" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ89" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA89" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BB89" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC89" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD89" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE89" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BF89" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG89" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17820,49 +17820,49 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G90" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H90" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I90" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J90" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="K90" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L90" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M90" t="n">
         <v>1.01</v>
       </c>
       <c r="N90" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O90" t="n">
         <v>1.02</v>
       </c>
       <c r="P90" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="R90" t="n">
         <v>1.18</v>
@@ -17877,10 +17877,10 @@
         <v>1.11</v>
       </c>
       <c r="V90" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W90" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -17992,14 +17992,14 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18014,55 +18014,55 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Admira Wacker</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="G91" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="H91" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S91" t="n">
         <v>2.88</v>
-      </c>
-      <c r="K91" t="n">
-        <v>500</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S91" t="n">
-        <v>3.15</v>
       </c>
       <c r="T91" t="n">
         <v>1.11</v>
@@ -18071,16 +18071,16 @@
         <v>1.11</v>
       </c>
       <c r="V91" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="W91" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="X91" t="n">
         <v>1000</v>
       </c>
       <c r="Y91" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z91" t="n">
         <v>1000</v>
@@ -18089,10 +18089,10 @@
         <v>1000</v>
       </c>
       <c r="AB91" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC91" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD91" t="n">
         <v>1000</v>
@@ -18104,7 +18104,7 @@
         <v>1000</v>
       </c>
       <c r="AG91" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH91" t="n">
         <v>1000</v>
@@ -18131,69 +18131,69 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU91" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY91" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ91" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BF91" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BG91" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18208,55 +18208,55 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Admira Wacker</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="G92" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="H92" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="I92" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K92" t="n">
-        <v>8.800000000000001</v>
+        <v>500</v>
       </c>
       <c r="L92" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M92" t="n">
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="O92" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P92" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R92" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S92" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T92" t="n">
         <v>1.11</v>
@@ -18265,10 +18265,10 @@
         <v>1.11</v>
       </c>
       <c r="V92" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W92" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -18402,179 +18402,179 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="G93" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="J93" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="K93" t="n">
-        <v>640</v>
+        <v>590</v>
       </c>
       <c r="L93" t="n">
         <v>1.01</v>
       </c>
       <c r="M93" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N93" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O93" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="P93" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="Q93" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="R93" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S93" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="T93" t="n">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U93" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V93" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="W93" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="X93" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y93" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z93" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA93" t="n">
         <v>1000</v>
       </c>
       <c r="AB93" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC93" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD93" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE93" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF93" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG93" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH93" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI93" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ93" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK93" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL93" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM93" t="n">
         <v>1000</v>
       </c>
       <c r="AN93" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO93" t="n">
         <v>1000</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AQ93" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="AS93" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AU93" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AV93" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW93" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX93" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY93" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AZ93" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BA93" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB93" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BD93" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BE93" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BF93" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG93" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -18596,179 +18596,179 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.27</v>
+        <v>7.2</v>
       </c>
       <c r="G94" t="n">
-        <v>1.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H94" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S94" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V94" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X94" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU94" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I94" t="n">
-        <v>25</v>
-      </c>
-      <c r="J94" t="n">
+      <c r="AV94" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX94" t="n">
         <v>4.8</v>
       </c>
-      <c r="K94" t="n">
-        <v>590</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N94" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R94" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S94" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T94" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U94" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W94" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AY94" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ94" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA94" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB94" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC94" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD94" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE94" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF94" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG94" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -18841,10 +18841,10 @@
         <v>3.4</v>
       </c>
       <c r="T95" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U95" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="V95" t="n">
         <v>1.98</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19178,179 +19178,179 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="H97" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I97" t="n">
-        <v>1.56</v>
+        <v>6.2</v>
       </c>
       <c r="J97" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K97" t="n">
-        <v>4.9</v>
+        <v>640</v>
       </c>
       <c r="L97" t="n">
         <v>1.01</v>
       </c>
       <c r="M97" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N97" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O97" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="P97" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="S97" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="T97" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="U97" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="V97" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="W97" t="n">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="X97" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN97" t="n">
         <v>22</v>
       </c>
-      <c r="Y97" t="n">
+      <c r="AO97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF97" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z97" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF97" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG97" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH97" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI97" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>260</v>
-      </c>
-      <c r="AK97" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL97" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM97" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN97" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO97" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP97" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ97" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR97" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS97" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT97" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU97" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV97" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW97" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX97" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY97" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ97" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA97" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB97" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC97" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF97" t="n">
-        <v>5</v>
-      </c>
       <c r="BG97" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19599,7 +19599,7 @@
         <v>1.01</v>
       </c>
       <c r="N99" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O99" t="n">
         <v>1.26</v>
@@ -19614,7 +19614,7 @@
         <v>1.31</v>
       </c>
       <c r="S99" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T99" t="n">
         <v>1.11</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19769,7 +19769,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G100" t="n">
         <v>2.58</v>
@@ -19778,13 +19778,13 @@
         <v>3.2</v>
       </c>
       <c r="I100" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
         <v>3.05</v>
       </c>
       <c r="K100" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L100" t="n">
         <v>1.34</v>
@@ -19817,7 +19817,7 @@
         <v>1.11</v>
       </c>
       <c r="V100" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W100" t="n">
         <v>1.64</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         <v>1.32</v>
       </c>
       <c r="G101" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H101" t="n">
         <v>12</v>
@@ -19987,7 +19987,7 @@
         <v>1.03</v>
       </c>
       <c r="N101" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O101" t="n">
         <v>1.2</v>
@@ -19996,13 +19996,13 @@
         <v>2.52</v>
       </c>
       <c r="Q101" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R101" t="n">
         <v>1.61</v>
       </c>
-      <c r="R101" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S101" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T101" t="n">
         <v>2.08</v>
@@ -20062,10 +20062,10 @@
         <v>38</v>
       </c>
       <c r="AM101" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN101" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO101" t="n">
         <v>230</v>
@@ -20077,10 +20077,10 @@
         <v>32</v>
       </c>
       <c r="AR101" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS101" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT101" t="n">
         <v>9</v>
@@ -20092,7 +20092,7 @@
         <v>36</v>
       </c>
       <c r="AW101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX101" t="n">
         <v>7.6</v>
@@ -20101,10 +20101,10 @@
         <v>10</v>
       </c>
       <c r="AZ101" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA101" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB101" t="n">
         <v>9.199999999999999</v>
@@ -20116,17 +20116,17 @@
         <v>32</v>
       </c>
       <c r="BE101" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BF101" t="n">
         <v>4.3</v>
       </c>
       <c r="BG101" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -20381,7 +20381,7 @@
         <v>1.35</v>
       </c>
       <c r="P103" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q103" t="n">
         <v>1.96</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -20548,7 +20548,7 @@
         <v>1.81</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H104" t="n">
         <v>5.3</v>
@@ -20569,7 +20569,7 @@
         <v>1.08</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O104" t="n">
         <v>1.35</v>
@@ -20590,7 +20590,7 @@
         <v>1.95</v>
       </c>
       <c r="U104" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V104" t="n">
         <v>1.22</v>
@@ -20647,7 +20647,7 @@
         <v>130</v>
       </c>
       <c r="AN104" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO104" t="n">
         <v>85</v>
@@ -20689,7 +20689,7 @@
         <v>65</v>
       </c>
       <c r="BB104" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC104" t="n">
         <v>18</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G108" t="n">
         <v>1.51</v>
@@ -21330,7 +21330,7 @@
         <v>8.6</v>
       </c>
       <c r="I108" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J108" t="n">
         <v>4.4</v>
@@ -21351,7 +21351,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q108" t="n">
         <v>1.89</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G111" t="n">
         <v>2.52</v>
@@ -21912,13 +21912,13 @@
         <v>3.4</v>
       </c>
       <c r="I111" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J111" t="n">
         <v>3.15</v>
       </c>
       <c r="K111" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L111" t="n">
         <v>1.01</v>
@@ -21927,7 +21927,7 @@
         <v>1.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O111" t="n">
         <v>1.45</v>
@@ -21939,10 +21939,10 @@
         <v>2.3</v>
       </c>
       <c r="R111" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S111" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T111" t="n">
         <v>1.94</v>
@@ -21951,13 +21951,13 @@
         <v>1.88</v>
       </c>
       <c r="V111" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W111" t="n">
         <v>1.66</v>
       </c>
       <c r="X111" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y111" t="n">
         <v>11.5</v>
@@ -21969,7 +21969,7 @@
         <v>1000</v>
       </c>
       <c r="AB111" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC111" t="n">
         <v>7.8</v>
@@ -22020,7 +22020,7 @@
         <v>20</v>
       </c>
       <c r="AS111" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT111" t="n">
         <v>7</v>
@@ -22032,7 +22032,7 @@
         <v>13</v>
       </c>
       <c r="AW111" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX111" t="n">
         <v>12</v>
@@ -22041,39 +22041,39 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ111" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA111" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB111" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC111" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC111" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD111" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE111" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF111" t="n">
         <v>21</v>
       </c>
       <c r="BG111" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -22088,31 +22088,31 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="G112" t="n">
-        <v>1.57</v>
+        <v>600</v>
       </c>
       <c r="H112" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I112" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="J112" t="n">
-        <v>4.3</v>
+        <v>1.09</v>
       </c>
       <c r="K112" t="n">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L112" t="n">
         <v>1.01</v>
@@ -22121,22 +22121,22 @@
         <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>2.94</v>
+        <v>1.1</v>
       </c>
       <c r="O112" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="P112" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.9</v>
+        <v>1.15</v>
       </c>
       <c r="R112" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S112" t="n">
-        <v>2.8</v>
+        <v>1.15</v>
       </c>
       <c r="T112" t="n">
         <v>1.11</v>
@@ -22145,10 +22145,10 @@
         <v>1.11</v>
       </c>
       <c r="V112" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W112" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="X112" t="n">
         <v>1000</v>
@@ -22205,52 +22205,52 @@
         <v>1000</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE112" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF112" t="n">
         <v>1.01</v>
@@ -22260,14 +22260,14 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22282,31 +22282,31 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="G113" t="n">
-        <v>600</v>
+        <v>1.57</v>
       </c>
       <c r="H113" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I113" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J113" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="K113" t="n">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L113" t="n">
         <v>1.01</v>
@@ -22315,22 +22315,22 @@
         <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>1.26</v>
+        <v>2.94</v>
       </c>
       <c r="O113" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="P113" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.15</v>
+        <v>1.9</v>
       </c>
       <c r="R113" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S113" t="n">
-        <v>1.16</v>
+        <v>2.8</v>
       </c>
       <c r="T113" t="n">
         <v>1.11</v>
@@ -22339,10 +22339,10 @@
         <v>1.11</v>
       </c>
       <c r="V113" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W113" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="X113" t="n">
         <v>1000</v>
@@ -22399,52 +22399,52 @@
         <v>1000</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE113" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF113" t="n">
         <v>1.01</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,395 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J115" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K115" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X115" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>2026-04-02 01:54:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K116" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V116" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
